--- a/research/traditional_assets/database/data/macau/macau_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_retail_distributors.xlsx
@@ -587,23 +587,26 @@
           <t>Retail (Distributors)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.206</v>
+      </c>
       <c r="G2">
-        <v>-3.290488431876607</v>
+        <v>-0.758364312267658</v>
       </c>
       <c r="H2">
-        <v>-3.303341902313624</v>
+        <v>-0.758364312267658</v>
       </c>
       <c r="I2">
-        <v>-3.622837115803393</v>
+        <v>-0.3990731401876629</v>
       </c>
       <c r="J2">
-        <v>-3.622837115803393</v>
+        <v>-0.3990731401876629</v>
       </c>
       <c r="K2">
-        <v>-2.98</v>
+        <v>-1.09</v>
       </c>
       <c r="L2">
-        <v>-3.830334190231362</v>
+        <v>-0.4052044609665428</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,61 +636,61 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.08333039402867772</v>
+        <v>0.07160210470809505</v>
       </c>
       <c r="Z2">
-        <v>16.26377230617017</v>
+        <v>18.23311794041307</v>
       </c>
       <c r="AA2">
-        <v>-58.92099795376866</v>
+        <v>-7.276347631892655</v>
       </c>
       <c r="AB2">
-        <v>0.08080352389340356</v>
+        <v>0.07024357453208108</v>
       </c>
       <c r="AC2">
-        <v>-59.00180147766206</v>
+        <v>-7.346591206424736</v>
       </c>
       <c r="AD2">
-        <v>0.246</v>
+        <v>0.123</v>
       </c>
       <c r="AE2">
-        <v>0.04783638047520139</v>
+        <v>0.1475337355240658</v>
       </c>
       <c r="AF2">
-        <v>0.2938363804752014</v>
+        <v>0.2705337355240658</v>
       </c>
       <c r="AG2">
-        <v>0.2938363804752014</v>
+        <v>0.2705337355240658</v>
       </c>
       <c r="AH2">
-        <v>0.07827628875982186</v>
+        <v>0.04584902784223093</v>
       </c>
       <c r="AI2">
-        <v>0.09030459621091597</v>
+        <v>0.1600285932420037</v>
       </c>
       <c r="AJ2">
-        <v>0.07827628875982186</v>
+        <v>0.04584902784223093</v>
       </c>
       <c r="AK2">
-        <v>0.09030459621091597</v>
+        <v>0.1600285932420037</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="AN2">
-        <v>-0.08916274012323305</v>
+        <v>-0.121301775147929</v>
       </c>
       <c r="AO2">
-        <v>-220</v>
+        <v>-171.4285714285714</v>
       </c>
       <c r="AP2">
-        <v>-0.1065010440287066</v>
+        <v>-0.2667985557436546</v>
       </c>
       <c r="AQ2">
-        <v>-238.3333333333333</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="3">
@@ -706,23 +709,26 @@
           <t>Retail (Distributors)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.206</v>
+      </c>
       <c r="G3">
-        <v>-3.290488431876607</v>
+        <v>-0.758364312267658</v>
       </c>
       <c r="H3">
-        <v>-3.303341902313624</v>
+        <v>-0.758364312267658</v>
       </c>
       <c r="I3">
-        <v>-3.622837115803393</v>
+        <v>-0.3990731401876629</v>
       </c>
       <c r="J3">
-        <v>-3.622837115803393</v>
+        <v>-0.3990731401876629</v>
       </c>
       <c r="K3">
-        <v>-2.98</v>
+        <v>-1.09</v>
       </c>
       <c r="L3">
-        <v>-3.830334190231362</v>
+        <v>-0.4052044609665428</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,61 +758,61 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08333039402867772</v>
+        <v>0.07160210470809505</v>
       </c>
       <c r="Z3">
-        <v>16.26377230617017</v>
+        <v>18.23311794041307</v>
       </c>
       <c r="AA3">
-        <v>-58.92099795376866</v>
+        <v>-7.276347631892655</v>
       </c>
       <c r="AB3">
-        <v>0.08080352389340356</v>
+        <v>0.07024357453208108</v>
       </c>
       <c r="AC3">
-        <v>-59.00180147766206</v>
+        <v>-7.346591206424736</v>
       </c>
       <c r="AD3">
-        <v>0.246</v>
+        <v>0.123</v>
       </c>
       <c r="AE3">
-        <v>0.04783638047520139</v>
+        <v>0.1475337355240658</v>
       </c>
       <c r="AF3">
-        <v>0.2938363804752014</v>
+        <v>0.2705337355240658</v>
       </c>
       <c r="AG3">
-        <v>0.2938363804752014</v>
+        <v>0.2705337355240658</v>
       </c>
       <c r="AH3">
-        <v>0.07827628875982186</v>
+        <v>0.04584902784223093</v>
       </c>
       <c r="AI3">
-        <v>0.09030459621091597</v>
+        <v>0.1600285932420037</v>
       </c>
       <c r="AJ3">
-        <v>0.07827628875982186</v>
+        <v>0.04584902784223093</v>
       </c>
       <c r="AK3">
-        <v>0.09030459621091597</v>
+        <v>0.1600285932420037</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
-        <v>-0.08916274012323305</v>
+        <v>-0.121301775147929</v>
       </c>
       <c r="AO3">
-        <v>-220</v>
+        <v>-171.4285714285714</v>
       </c>
       <c r="AP3">
-        <v>-0.1065010440287066</v>
+        <v>-0.2667985557436546</v>
       </c>
       <c r="AQ3">
-        <v>-238.3333333333333</v>
+        <v>-600</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/macau/macau_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_retail_distributors.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07548465725062632</v>
+        <v>0.07531481846125114</v>
       </c>
       <c r="C2">
-        <v>6.54441521881518</v>
+        <v>6.489903993737395</v>
       </c>
       <c r="D2">
-        <v>4.77441521881518</v>
+        <v>4.785736803617321</v>
       </c>
       <c r="E2">
-        <v>-0.5332809879927326</v>
+        <v>-0.4674481781128053</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.06583280987992732</v>
       </c>
       <c r="G2">
         <v>1.77</v>
@@ -1445,28 +1445,28 @@
         <v>0.497</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.003311390336960344</v>
       </c>
       <c r="N2">
-        <v>0.497</v>
+        <v>0.4936886096630397</v>
       </c>
       <c r="O2">
-        <v>0.1334942</v>
+        <v>0.1326047605554925</v>
       </c>
       <c r="P2">
-        <v>0.3635058</v>
+        <v>0.3610838491075472</v>
       </c>
       <c r="Q2">
-        <v>0.4435058</v>
+        <v>0.4410838491075472</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07548465725062632</v>
+        <v>0.07570396390025368</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5828839166346815</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.088014225534</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07531481846125114</v>
+        <v>0.07514497967187596</v>
       </c>
       <c r="C3">
-        <v>6.489903993737395</v>
+        <v>6.435446590100997</v>
       </c>
       <c r="D3">
-        <v>4.785736803617321</v>
+        <v>4.797112209860852</v>
       </c>
       <c r="E3">
-        <v>-0.4674481781128053</v>
+        <v>-0.401615368232878</v>
       </c>
       <c r="F3">
-        <v>0.06583280987992732</v>
+        <v>0.1316656197598546</v>
       </c>
       <c r="G3">
         <v>1.77</v>
@@ -1527,28 +1527,28 @@
         <v>0.497</v>
       </c>
       <c r="M3">
-        <v>0.003311390336960344</v>
+        <v>0.006622780673920687</v>
       </c>
       <c r="N3">
-        <v>0.4936886096630397</v>
+        <v>0.4903772193260793</v>
       </c>
       <c r="O3">
-        <v>0.1326047605554925</v>
+        <v>0.1317153211109849</v>
       </c>
       <c r="P3">
-        <v>0.3610838491075472</v>
+        <v>0.3586618982150944</v>
       </c>
       <c r="Q3">
-        <v>0.4410838491075472</v>
+        <v>0.4386618982150944</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07570396390025368</v>
+        <v>0.07592774619579179</v>
       </c>
       <c r="T3">
-        <v>0.5828839166346815</v>
+        <v>0.5872458501004871</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.088014225534</v>
+        <v>75.04400711276702</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07514497967187596</v>
+        <v>0.07497514088250079</v>
       </c>
       <c r="C4">
-        <v>6.435446590100997</v>
+        <v>6.381043392611322</v>
       </c>
       <c r="D4">
-        <v>4.797112209860852</v>
+        <v>4.808541822251104</v>
       </c>
       <c r="E4">
-        <v>-0.401615368232878</v>
+        <v>-0.3357825583529507</v>
       </c>
       <c r="F4">
-        <v>0.1316656197598546</v>
+        <v>0.197498429639782</v>
       </c>
       <c r="G4">
         <v>1.77</v>
@@ -1609,28 +1609,28 @@
         <v>0.497</v>
       </c>
       <c r="M4">
-        <v>0.006622780673920687</v>
+        <v>0.009934171010881033</v>
       </c>
       <c r="N4">
-        <v>0.4903772193260793</v>
+        <v>0.487065828989119</v>
       </c>
       <c r="O4">
-        <v>0.1317153211109849</v>
+        <v>0.1308258816664774</v>
       </c>
       <c r="P4">
-        <v>0.3586618982150944</v>
+        <v>0.3562399473226416</v>
       </c>
       <c r="Q4">
-        <v>0.4386618982150944</v>
+        <v>0.4362399473226416</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07592774619579179</v>
+        <v>0.07615614255927916</v>
       </c>
       <c r="T4">
-        <v>0.5872458501004871</v>
+        <v>0.5916977203387835</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.04400711276702</v>
+        <v>50.029338075178</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07497514088250079</v>
+        <v>0.07480530209312558</v>
       </c>
       <c r="C5">
-        <v>6.381043392611322</v>
+        <v>6.326694789648861</v>
       </c>
       <c r="D5">
-        <v>4.808541822251104</v>
+        <v>4.820026029168569</v>
       </c>
       <c r="E5">
-        <v>-0.3357825583529507</v>
+        <v>-0.2699497484730233</v>
       </c>
       <c r="F5">
-        <v>0.197498429639782</v>
+        <v>0.2633312395197093</v>
       </c>
       <c r="G5">
         <v>1.77</v>
@@ -1691,28 +1691,28 @@
         <v>0.497</v>
       </c>
       <c r="M5">
-        <v>0.009934171010881033</v>
+        <v>0.01324556134784137</v>
       </c>
       <c r="N5">
-        <v>0.487065828989119</v>
+        <v>0.4837544386521586</v>
       </c>
       <c r="O5">
-        <v>0.1308258816664774</v>
+        <v>0.1299364422219698</v>
       </c>
       <c r="P5">
-        <v>0.3562399473226416</v>
+        <v>0.3538179964301888</v>
       </c>
       <c r="Q5">
-        <v>0.4362399473226416</v>
+        <v>0.4338179964301888</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07615614255927916</v>
+        <v>0.07638929718033916</v>
       </c>
       <c r="T5">
-        <v>0.5916977203387835</v>
+        <v>0.5962423378737111</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.029338075178</v>
+        <v>37.52200355638351</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07480530209312558</v>
+        <v>0.07463546330375041</v>
       </c>
       <c r="C6">
-        <v>6.326694789648861</v>
+        <v>6.27240117331324</v>
       </c>
       <c r="D6">
-        <v>4.820026029168569</v>
+        <v>4.831565222712876</v>
       </c>
       <c r="E6">
-        <v>-0.2699497484730233</v>
+        <v>-0.204116938593096</v>
       </c>
       <c r="F6">
-        <v>0.2633312395197093</v>
+        <v>0.3291640493996366</v>
       </c>
       <c r="G6">
         <v>1.77</v>
@@ -1773,28 +1773,28 @@
         <v>0.497</v>
       </c>
       <c r="M6">
-        <v>0.01324556134784137</v>
+        <v>0.01655695168480172</v>
       </c>
       <c r="N6">
-        <v>0.4837544386521586</v>
+        <v>0.4804430483151983</v>
       </c>
       <c r="O6">
-        <v>0.1299364422219698</v>
+        <v>0.1290470027774623</v>
       </c>
       <c r="P6">
-        <v>0.3538179964301888</v>
+        <v>0.3513960455377361</v>
       </c>
       <c r="Q6">
-        <v>0.4338179964301888</v>
+        <v>0.431396045537736</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07638929718033916</v>
+        <v>0.07662736031973728</v>
       </c>
       <c r="T6">
-        <v>0.5962423378737111</v>
+        <v>0.6008826315672687</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.52200355638351</v>
+        <v>30.0176028451068</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07463546330375041</v>
+        <v>0.07446562451437523</v>
       </c>
       <c r="C7">
-        <v>6.27240117331324</v>
+        <v>6.218162939467872</v>
       </c>
       <c r="D7">
-        <v>4.831565222712876</v>
+        <v>4.843159798747436</v>
       </c>
       <c r="E7">
-        <v>-0.204116938593096</v>
+        <v>-0.1382841287131686</v>
       </c>
       <c r="F7">
-        <v>0.3291640493996366</v>
+        <v>0.394996859279564</v>
       </c>
       <c r="G7">
         <v>1.77</v>
@@ -1855,28 +1855,28 @@
         <v>0.497</v>
       </c>
       <c r="M7">
-        <v>0.01655695168480172</v>
+        <v>0.01986834202176207</v>
       </c>
       <c r="N7">
-        <v>0.4804430483151983</v>
+        <v>0.4771316579782379</v>
       </c>
       <c r="O7">
-        <v>0.1290470027774623</v>
+        <v>0.1281575633329547</v>
       </c>
       <c r="P7">
-        <v>0.3513960455377361</v>
+        <v>0.3489740946452832</v>
       </c>
       <c r="Q7">
-        <v>0.431396045537736</v>
+        <v>0.4289740946452831</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07662736031973728</v>
+        <v>0.07687048863231408</v>
       </c>
       <c r="T7">
-        <v>0.6008826315672687</v>
+        <v>0.6056216549138808</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.0176028451068</v>
+        <v>25.014669037589</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07446562451437523</v>
+        <v>0.07429578572500005</v>
       </c>
       <c r="C8">
-        <v>6.218162939467872</v>
+        <v>6.16398048778521</v>
       </c>
       <c r="D8">
-        <v>4.843159798747436</v>
+        <v>4.8548101569447</v>
       </c>
       <c r="E8">
-        <v>-0.1382841287131687</v>
+        <v>-0.07245131883324141</v>
       </c>
       <c r="F8">
-        <v>0.3949968592795639</v>
+        <v>0.4608296691594912</v>
       </c>
       <c r="G8">
         <v>1.77</v>
@@ -1937,28 +1937,28 @@
         <v>0.497</v>
       </c>
       <c r="M8">
-        <v>0.01986834202176207</v>
+        <v>0.02317973235872241</v>
       </c>
       <c r="N8">
-        <v>0.4771316579782379</v>
+        <v>0.4738202676412776</v>
       </c>
       <c r="O8">
-        <v>0.1281575633329547</v>
+        <v>0.1272681238884472</v>
       </c>
       <c r="P8">
-        <v>0.3489740946452832</v>
+        <v>0.3465521437528304</v>
       </c>
       <c r="Q8">
-        <v>0.4289740946452831</v>
+        <v>0.4265521437528304</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07687048863231408</v>
+        <v>0.07711884551075274</v>
       </c>
       <c r="T8">
-        <v>0.6056216549138808</v>
+        <v>0.610462592741065</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.014669037589</v>
+        <v>21.441144889362</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07429578572500005</v>
+        <v>0.07412594693562487</v>
       </c>
       <c r="C9">
-        <v>6.16398048778521</v>
+        <v>6.109854221792669</v>
       </c>
       <c r="D9">
-        <v>4.8548101569447</v>
+        <v>4.866516700832088</v>
       </c>
       <c r="E9">
-        <v>-0.0724513188332413</v>
+        <v>-0.006618508953314062</v>
       </c>
       <c r="F9">
-        <v>0.4608296691594913</v>
+        <v>0.5266624790394185</v>
       </c>
       <c r="G9">
         <v>1.77</v>
@@ -2019,28 +2019,28 @@
         <v>0.497</v>
       </c>
       <c r="M9">
-        <v>0.02317973235872241</v>
+        <v>0.02649112269568275</v>
       </c>
       <c r="N9">
-        <v>0.4738202676412776</v>
+        <v>0.4705088773043172</v>
       </c>
       <c r="O9">
-        <v>0.1272681238884472</v>
+        <v>0.1263786844439396</v>
       </c>
       <c r="P9">
-        <v>0.3465521437528304</v>
+        <v>0.3441301928603776</v>
       </c>
       <c r="Q9">
-        <v>0.4265521437528304</v>
+        <v>0.4241301928603776</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07711884551075274</v>
+        <v>0.07737260145176617</v>
       </c>
       <c r="T9">
-        <v>0.6104625927410651</v>
+        <v>0.6154087683471012</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.441144889362</v>
+        <v>18.76100177819175</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07412594693562487</v>
+        <v>0.07395610814624969</v>
       </c>
       <c r="C10">
-        <v>6.109854221792669</v>
+        <v>6.055784548919227</v>
       </c>
       <c r="D10">
-        <v>4.866516700832088</v>
+        <v>4.878279837838573</v>
       </c>
       <c r="E10">
-        <v>-0.006618508953314062</v>
+        <v>0.05921430092661328</v>
       </c>
       <c r="F10">
-        <v>0.5266624790394185</v>
+        <v>0.5924952889193459</v>
       </c>
       <c r="G10">
         <v>1.77</v>
@@ -2101,28 +2101,28 @@
         <v>0.497</v>
       </c>
       <c r="M10">
-        <v>0.02649112269568275</v>
+        <v>0.0298025130326431</v>
       </c>
       <c r="N10">
-        <v>0.4705088773043172</v>
+        <v>0.4671974869673569</v>
       </c>
       <c r="O10">
-        <v>0.1263786844439396</v>
+        <v>0.1254892449994321</v>
       </c>
       <c r="P10">
-        <v>0.3441301928603776</v>
+        <v>0.3417082419679248</v>
       </c>
       <c r="Q10">
-        <v>0.4241301928603776</v>
+        <v>0.4217082419679248</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07737260145176617</v>
+        <v>0.07763193444642823</v>
       </c>
       <c r="T10">
-        <v>0.6154087683471012</v>
+        <v>0.620463651109314</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.76100177819175</v>
+        <v>16.67644602505933</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07395610814624969</v>
+        <v>0.07378626935687452</v>
       </c>
       <c r="C11">
-        <v>6.055784548919227</v>
+        <v>6.001771880542679</v>
       </c>
       <c r="D11">
-        <v>4.878279837838573</v>
+        <v>4.890099979341953</v>
       </c>
       <c r="E11">
-        <v>0.05921430092661328</v>
+        <v>0.1250471108065406</v>
       </c>
       <c r="F11">
-        <v>0.5924952889193459</v>
+        <v>0.6583280987992732</v>
       </c>
       <c r="G11">
         <v>1.77</v>
@@ -2183,28 +2183,28 @@
         <v>0.497</v>
       </c>
       <c r="M11">
-        <v>0.0298025130326431</v>
+        <v>0.03311390336960345</v>
       </c>
       <c r="N11">
-        <v>0.4671974869673569</v>
+        <v>0.4638860966303965</v>
       </c>
       <c r="O11">
-        <v>0.1254892449994321</v>
+        <v>0.1245998055549245</v>
       </c>
       <c r="P11">
-        <v>0.3417082419679248</v>
+        <v>0.339286291075472</v>
       </c>
       <c r="Q11">
-        <v>0.4217082419679248</v>
+        <v>0.419286291075472</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07763193444642823</v>
+        <v>0.07789703039652723</v>
       </c>
       <c r="T11">
-        <v>0.620463651109314</v>
+        <v>0.625630864599576</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.67644602505933</v>
+        <v>15.0088014225534</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07378626935687452</v>
+        <v>0.07361643056749932</v>
       </c>
       <c r="C12">
-        <v>6.001771880542679</v>
+        <v>5.947816632037613</v>
       </c>
       <c r="D12">
-        <v>4.890099979341953</v>
+        <v>4.901977540716814</v>
       </c>
       <c r="E12">
-        <v>0.1250471108065406</v>
+        <v>0.190879920686468</v>
       </c>
       <c r="F12">
-        <v>0.6583280987992732</v>
+        <v>0.7241609086792006</v>
       </c>
       <c r="G12">
         <v>1.77</v>
@@ -2265,28 +2265,28 @@
         <v>0.497</v>
       </c>
       <c r="M12">
-        <v>0.03311390336960345</v>
+        <v>0.03642529370656378</v>
       </c>
       <c r="N12">
-        <v>0.4638860966303965</v>
+        <v>0.4605747062934362</v>
       </c>
       <c r="O12">
-        <v>0.1245998055549245</v>
+        <v>0.123710366110417</v>
       </c>
       <c r="P12">
-        <v>0.339286291075472</v>
+        <v>0.3368643401830193</v>
       </c>
       <c r="Q12">
-        <v>0.419286291075472</v>
+        <v>0.4168643401830192</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07789703039652723</v>
+        <v>0.07816808355898799</v>
       </c>
       <c r="T12">
-        <v>0.625630864599576</v>
+        <v>0.6309141952469224</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.0088014225534</v>
+        <v>13.644364929594</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07361643056749932</v>
+        <v>0.07357824377812414</v>
       </c>
       <c r="C13">
-        <v>5.947816632037613</v>
+        <v>5.88466233888346</v>
       </c>
       <c r="D13">
-        <v>4.901977540716814</v>
+        <v>4.904656057442589</v>
       </c>
       <c r="E13">
-        <v>0.190879920686468</v>
+        <v>0.2567127305663952</v>
       </c>
       <c r="F13">
-        <v>0.7241609086792006</v>
+        <v>0.7899937185591278</v>
       </c>
       <c r="G13">
         <v>1.77</v>
@@ -2347,45 +2347,45 @@
         <v>0.497</v>
       </c>
       <c r="M13">
-        <v>0.03642529370656378</v>
+        <v>0.04092167462136282</v>
       </c>
       <c r="N13">
-        <v>0.4605747062934362</v>
+        <v>0.4560783253786372</v>
       </c>
       <c r="O13">
-        <v>0.123710366110417</v>
+        <v>0.1225026381967019</v>
       </c>
       <c r="P13">
-        <v>0.3368643401830193</v>
+        <v>0.3335756871819353</v>
       </c>
       <c r="Q13">
-        <v>0.4168643401830192</v>
+        <v>0.4135756871819352</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07816808355898799</v>
+        <v>0.07844529702059561</v>
       </c>
       <c r="T13">
-        <v>0.6309141952469224</v>
+        <v>0.6363176015907995</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.2686</v>
       </c>
       <c r="W13">
-        <v>0.03678942</v>
+        <v>0.03788652</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.644364929594</v>
+        <v>12.14515301728501</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07357824377812414</v>
+        <v>0.07341937598874895</v>
       </c>
       <c r="C14">
-        <v>5.88466233888346</v>
+        <v>5.83000440442289</v>
       </c>
       <c r="D14">
-        <v>4.904656057442589</v>
+        <v>4.915830932861946</v>
       </c>
       <c r="E14">
-        <v>0.2567127305663952</v>
+        <v>0.3225455404463227</v>
       </c>
       <c r="F14">
-        <v>0.7899937185591278</v>
+        <v>0.8558265284390553</v>
       </c>
       <c r="G14">
         <v>1.77</v>
@@ -2429,28 +2429,28 @@
         <v>0.497</v>
       </c>
       <c r="M14">
-        <v>0.04092167462136282</v>
+        <v>0.04433181417314306</v>
       </c>
       <c r="N14">
-        <v>0.4560783253786372</v>
+        <v>0.4526681858268569</v>
       </c>
       <c r="O14">
-        <v>0.1225026381967019</v>
+        <v>0.1215866747130938</v>
       </c>
       <c r="P14">
-        <v>0.3335756871819353</v>
+        <v>0.3310815111137632</v>
       </c>
       <c r="Q14">
-        <v>0.4135756871819352</v>
+        <v>0.4110815111137631</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07844529702059561</v>
+        <v>0.07872888320545857</v>
       </c>
       <c r="T14">
-        <v>0.6363176015907995</v>
+        <v>0.6418452241724669</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.14515301728501</v>
+        <v>11.21091047749385</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07341937598874895</v>
+        <v>0.07326050819937377</v>
       </c>
       <c r="C15">
-        <v>5.83000440442289</v>
+        <v>5.775397508409591</v>
       </c>
       <c r="D15">
-        <v>4.915830932861946</v>
+        <v>4.927056846728574</v>
       </c>
       <c r="E15">
-        <v>0.3225455404463227</v>
+        <v>0.38837835032625</v>
       </c>
       <c r="F15">
-        <v>0.8558265284390553</v>
+        <v>0.9216593383189826</v>
       </c>
       <c r="G15">
         <v>1.77</v>
@@ -2511,28 +2511,28 @@
         <v>0.497</v>
       </c>
       <c r="M15">
-        <v>0.04433181417314306</v>
+        <v>0.0477419537249233</v>
       </c>
       <c r="N15">
-        <v>0.4526681858268569</v>
+        <v>0.4492580462750767</v>
       </c>
       <c r="O15">
-        <v>0.1215866747130938</v>
+        <v>0.1206707112294856</v>
       </c>
       <c r="P15">
-        <v>0.3310815111137632</v>
+        <v>0.3285873350455911</v>
       </c>
       <c r="Q15">
-        <v>0.4110815111137631</v>
+        <v>0.4085873350455911</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07872888320545857</v>
+        <v>0.07901906441787648</v>
       </c>
       <c r="T15">
-        <v>0.6418452241724669</v>
+        <v>0.6475013961164986</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.21091047749385</v>
+        <v>10.41013115767286</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07326050819937377</v>
+        <v>0.0732881474099986</v>
       </c>
       <c r="C16">
-        <v>5.775397508409591</v>
+        <v>5.707607974338148</v>
       </c>
       <c r="D16">
-        <v>4.927056846728574</v>
+        <v>4.925100122537058</v>
       </c>
       <c r="E16">
-        <v>0.38837835032625</v>
+        <v>0.4542111602061774</v>
       </c>
       <c r="F16">
-        <v>0.9216593383189826</v>
+        <v>0.98749214819891</v>
       </c>
       <c r="G16">
         <v>1.77</v>
@@ -2593,45 +2593,45 @@
         <v>0.497</v>
       </c>
       <c r="M16">
-        <v>0.0477419537249233</v>
+        <v>0.05283082992864168</v>
       </c>
       <c r="N16">
-        <v>0.4492580462750767</v>
+        <v>0.4441691700713583</v>
       </c>
       <c r="O16">
-        <v>0.1206707112294856</v>
+        <v>0.1193038390811668</v>
       </c>
       <c r="P16">
-        <v>0.3285873350455911</v>
+        <v>0.3248653309901914</v>
       </c>
       <c r="Q16">
-        <v>0.4085873350455911</v>
+        <v>0.4048653309901914</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07901906441787648</v>
+        <v>0.07931607342352776</v>
       </c>
       <c r="T16">
-        <v>0.6475013961164986</v>
+        <v>0.6532906544592135</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.2686</v>
       </c>
       <c r="W16">
-        <v>0.03788652</v>
+        <v>0.0391299</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.41013115767286</v>
+        <v>9.407385813762442</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07328814740999859</v>
+        <v>0.07314171342062341</v>
       </c>
       <c r="C17">
-        <v>5.70760797433815</v>
+        <v>5.652159724663054</v>
       </c>
       <c r="D17">
-        <v>4.92510012253706</v>
+        <v>4.935484682741891</v>
       </c>
       <c r="E17">
-        <v>0.4542111602061772</v>
+        <v>0.5200439700861045</v>
       </c>
       <c r="F17">
-        <v>0.9874921481989098</v>
+        <v>1.053324958078837</v>
       </c>
       <c r="G17">
         <v>1.77</v>
@@ -2675,28 +2675,28 @@
         <v>0.497</v>
       </c>
       <c r="M17">
-        <v>0.05283082992864167</v>
+        <v>0.05635288525721778</v>
       </c>
       <c r="N17">
-        <v>0.4441691700713583</v>
+        <v>0.4406471147427822</v>
       </c>
       <c r="O17">
-        <v>0.1193038390811668</v>
+        <v>0.1183578150199113</v>
       </c>
       <c r="P17">
-        <v>0.3248653309901914</v>
+        <v>0.3222892997228709</v>
       </c>
       <c r="Q17">
-        <v>0.4048653309901914</v>
+        <v>0.4022892997228709</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07931607342352776</v>
+        <v>0.07962015407217073</v>
       </c>
       <c r="T17">
-        <v>0.6532906544592134</v>
+        <v>0.6592177522862787</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.407385813762444</v>
+        <v>8.819424200402292</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07314171342062341</v>
+        <v>0.07299527943124823</v>
       </c>
       <c r="C18">
-        <v>5.652159724663054</v>
+        <v>5.596755359151459</v>
       </c>
       <c r="D18">
-        <v>4.935484682741891</v>
+        <v>4.945913127110223</v>
       </c>
       <c r="E18">
-        <v>0.5200439700861045</v>
+        <v>0.5858767799660319</v>
       </c>
       <c r="F18">
-        <v>1.053324958078837</v>
+        <v>1.119157767958765</v>
       </c>
       <c r="G18">
         <v>1.77</v>
@@ -2757,28 +2757,28 @@
         <v>0.497</v>
       </c>
       <c r="M18">
-        <v>0.05635288525721778</v>
+        <v>0.0598749405857939</v>
       </c>
       <c r="N18">
-        <v>0.4406471147427822</v>
+        <v>0.4371250594142061</v>
       </c>
       <c r="O18">
-        <v>0.1183578150199113</v>
+        <v>0.1174117909586558</v>
       </c>
       <c r="P18">
-        <v>0.3222892997228709</v>
+        <v>0.3197132684555504</v>
       </c>
       <c r="Q18">
-        <v>0.4022892997228709</v>
+        <v>0.3997132684555503</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07962015407217073</v>
+        <v>0.0799315619653593</v>
       </c>
       <c r="T18">
-        <v>0.6592177522862787</v>
+        <v>0.665287671747731</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.819424200402292</v>
+        <v>8.300634541555096</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07299527943124823</v>
+        <v>0.07284884544187303</v>
       </c>
       <c r="C19">
-        <v>5.596755359151459</v>
+        <v>5.541395156567832</v>
       </c>
       <c r="D19">
-        <v>4.945913127110223</v>
+        <v>4.956385734406523</v>
       </c>
       <c r="E19">
-        <v>0.5858767799660319</v>
+        <v>0.6517095898459594</v>
       </c>
       <c r="F19">
-        <v>1.119157767958765</v>
+        <v>1.184990577838692</v>
       </c>
       <c r="G19">
         <v>1.77</v>
@@ -2839,28 +2839,28 @@
         <v>0.497</v>
       </c>
       <c r="M19">
-        <v>0.0598749405857939</v>
+        <v>0.06339699591437002</v>
       </c>
       <c r="N19">
-        <v>0.4371250594142061</v>
+        <v>0.43360300408563</v>
       </c>
       <c r="O19">
-        <v>0.1174117909586558</v>
+        <v>0.1164657668974002</v>
       </c>
       <c r="P19">
-        <v>0.3197132684555504</v>
+        <v>0.3171372371882297</v>
       </c>
       <c r="Q19">
-        <v>0.3997132684555503</v>
+        <v>0.3971372371882297</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0799315619653593</v>
+        <v>0.0802505651730159</v>
       </c>
       <c r="T19">
-        <v>0.665287671747731</v>
+        <v>0.6715056380253163</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.300634541555096</v>
+        <v>7.839488178135367</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07284884544187305</v>
+        <v>0.07281358425249787</v>
       </c>
       <c r="C20">
-        <v>5.54139515656783</v>
+        <v>5.478090771177464</v>
       </c>
       <c r="D20">
-        <v>4.956385734406521</v>
+        <v>4.958914158896084</v>
       </c>
       <c r="E20">
-        <v>0.6517095898459592</v>
+        <v>0.7175423997258866</v>
       </c>
       <c r="F20">
-        <v>1.184990577838692</v>
+        <v>1.250823387718619</v>
       </c>
       <c r="G20">
         <v>1.77</v>
@@ -2921,45 +2921,45 @@
         <v>0.497</v>
       </c>
       <c r="M20">
-        <v>0.06339699591437001</v>
+        <v>0.06791970995312102</v>
       </c>
       <c r="N20">
-        <v>0.43360300408563</v>
+        <v>0.429080290046879</v>
       </c>
       <c r="O20">
-        <v>0.1164657668974002</v>
+        <v>0.1152509659065917</v>
       </c>
       <c r="P20">
-        <v>0.3171372371882298</v>
+        <v>0.3138293241402873</v>
       </c>
       <c r="Q20">
-        <v>0.3971372371882297</v>
+        <v>0.3938293241402873</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0802505651730159</v>
+        <v>0.08057744500308378</v>
       </c>
       <c r="T20">
-        <v>0.6715056380253163</v>
+        <v>0.6778771343344467</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.2686</v>
       </c>
       <c r="W20">
-        <v>0.0391299</v>
+        <v>0.03971502</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.83948817813537</v>
+        <v>7.317463521900126</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07281358425249787</v>
+        <v>0.07267300146312268</v>
       </c>
       <c r="C21">
-        <v>5.478090771177464</v>
+        <v>5.422364230698794</v>
       </c>
       <c r="D21">
-        <v>4.958914158896084</v>
+        <v>4.96902042829734</v>
       </c>
       <c r="E21">
-        <v>0.7175423997258866</v>
+        <v>0.7833752096058139</v>
       </c>
       <c r="F21">
-        <v>1.250823387718619</v>
+        <v>1.316656197598546</v>
       </c>
       <c r="G21">
         <v>1.77</v>
@@ -3003,28 +3003,28 @@
         <v>0.497</v>
       </c>
       <c r="M21">
-        <v>0.06791970995312102</v>
+        <v>0.07149443152960107</v>
       </c>
       <c r="N21">
-        <v>0.429080290046879</v>
+        <v>0.4255055684703989</v>
       </c>
       <c r="O21">
-        <v>0.1152509659065917</v>
+        <v>0.1142907956911492</v>
       </c>
       <c r="P21">
-        <v>0.3138293241402873</v>
+        <v>0.3112147727792498</v>
       </c>
       <c r="Q21">
-        <v>0.3938293241402873</v>
+        <v>0.3912147727792498</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08057744500308378</v>
+        <v>0.08091249682890335</v>
       </c>
       <c r="T21">
-        <v>0.6778771343344467</v>
+        <v>0.6844079180513056</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.317463521900126</v>
+        <v>6.951590345805121</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07267300146312268</v>
+        <v>0.0725324186737475</v>
       </c>
       <c r="C22">
-        <v>5.422364230698794</v>
+        <v>5.366678967506889</v>
       </c>
       <c r="D22">
-        <v>4.96902042829734</v>
+        <v>4.979167974985364</v>
       </c>
       <c r="E22">
-        <v>0.7833752096058139</v>
+        <v>0.8492080194857413</v>
       </c>
       <c r="F22">
-        <v>1.316656197598546</v>
+        <v>1.382489007478474</v>
       </c>
       <c r="G22">
         <v>1.77</v>
@@ -3085,28 +3085,28 @@
         <v>0.497</v>
       </c>
       <c r="M22">
-        <v>0.07149443152960107</v>
+        <v>0.07506915310608113</v>
       </c>
       <c r="N22">
-        <v>0.4255055684703989</v>
+        <v>0.4219308468939189</v>
       </c>
       <c r="O22">
-        <v>0.1142907956911492</v>
+        <v>0.1133306254757066</v>
       </c>
       <c r="P22">
-        <v>0.3112147727792498</v>
+        <v>0.3086002214182123</v>
       </c>
       <c r="Q22">
-        <v>0.3912147727792498</v>
+        <v>0.3886002214182122</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08091249682890335</v>
+        <v>0.08125603097942721</v>
       </c>
       <c r="T22">
-        <v>0.6844079180513056</v>
+        <v>0.6911040380647938</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.951590345805121</v>
+        <v>6.620562234100114</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0725324186737475</v>
+        <v>0.07239183588437233</v>
       </c>
       <c r="C23">
-        <v>5.36667896750689</v>
+        <v>5.311035235004015</v>
       </c>
       <c r="D23">
-        <v>4.979167974985364</v>
+        <v>4.989357052362416</v>
       </c>
       <c r="E23">
-        <v>0.8492080194857411</v>
+        <v>0.9150408293656686</v>
       </c>
       <c r="F23">
-        <v>1.382489007478474</v>
+        <v>1.448321817358401</v>
       </c>
       <c r="G23">
         <v>1.77</v>
@@ -3167,28 +3167,28 @@
         <v>0.497</v>
       </c>
       <c r="M23">
-        <v>0.07506915310608113</v>
+        <v>0.07864387468256119</v>
       </c>
       <c r="N23">
-        <v>0.4219308468939189</v>
+        <v>0.4183561253174388</v>
       </c>
       <c r="O23">
-        <v>0.1133306254757066</v>
+        <v>0.1123704552602641</v>
       </c>
       <c r="P23">
-        <v>0.3086002214182123</v>
+        <v>0.3059856700571748</v>
       </c>
       <c r="Q23">
-        <v>0.3886002214182122</v>
+        <v>0.3859856700571747</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08125603097942721</v>
+        <v>0.08160837369791323</v>
       </c>
       <c r="T23">
-        <v>0.6911040380647938</v>
+        <v>0.6979718534632433</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.620562234100114</v>
+        <v>6.319627587095563</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07239183588437233</v>
+        <v>0.07241947509499715</v>
       </c>
       <c r="C24">
-        <v>5.311035235004015</v>
+        <v>5.243195914534333</v>
       </c>
       <c r="D24">
-        <v>4.989357052362416</v>
+        <v>4.987350541772661</v>
       </c>
       <c r="E24">
-        <v>0.9150408293656686</v>
+        <v>0.9808736392455958</v>
       </c>
       <c r="F24">
-        <v>1.448321817358401</v>
+        <v>1.514154627238328</v>
       </c>
       <c r="G24">
         <v>1.77</v>
@@ -3249,45 +3249,45 @@
         <v>0.497</v>
       </c>
       <c r="M24">
-        <v>0.07864387468256119</v>
+        <v>0.08373275088627956</v>
       </c>
       <c r="N24">
-        <v>0.4183561253174388</v>
+        <v>0.4132672491137204</v>
       </c>
       <c r="O24">
-        <v>0.1123704552602641</v>
+        <v>0.1110035831119453</v>
       </c>
       <c r="P24">
-        <v>0.3059856700571748</v>
+        <v>0.3022636660017751</v>
       </c>
       <c r="Q24">
-        <v>0.3859856700571747</v>
+        <v>0.3822636660017751</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08160837369791323</v>
+        <v>0.08196986817532095</v>
       </c>
       <c r="T24">
-        <v>0.6979718534632433</v>
+        <v>0.7050180536772368</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.2686</v>
       </c>
       <c r="W24">
-        <v>0.03971502</v>
+        <v>0.04044642</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.319627587095563</v>
+        <v>5.935550841689095</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07241947509499715</v>
+        <v>0.07228620630562196</v>
       </c>
       <c r="C25">
-        <v>5.243195914534333</v>
+        <v>5.187052853937519</v>
       </c>
       <c r="D25">
-        <v>4.987350541772661</v>
+        <v>4.997040291055775</v>
       </c>
       <c r="E25">
-        <v>0.9808736392455958</v>
+        <v>1.046706449125523</v>
       </c>
       <c r="F25">
-        <v>1.514154627238328</v>
+        <v>1.579987437118256</v>
       </c>
       <c r="G25">
         <v>1.77</v>
@@ -3331,28 +3331,28 @@
         <v>0.497</v>
       </c>
       <c r="M25">
-        <v>0.08373275088627956</v>
+        <v>0.08737330527263955</v>
       </c>
       <c r="N25">
-        <v>0.4132672491137204</v>
+        <v>0.4096266947273605</v>
       </c>
       <c r="O25">
-        <v>0.1110035831119453</v>
+        <v>0.110025730203769</v>
       </c>
       <c r="P25">
-        <v>0.3022636660017751</v>
+        <v>0.2996009645235914</v>
       </c>
       <c r="Q25">
-        <v>0.3822636660017751</v>
+        <v>0.3796009645235914</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08196986817532095</v>
+        <v>0.08234087566529205</v>
       </c>
       <c r="T25">
-        <v>0.7050180536772368</v>
+        <v>0.7122496802126513</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.935550841689095</v>
+        <v>5.688236223285383</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07228620630562195</v>
+        <v>0.07215293751624677</v>
       </c>
       <c r="C26">
-        <v>5.187052853937521</v>
+        <v>5.130947518386701</v>
       </c>
       <c r="D26">
-        <v>4.997040291055776</v>
+        <v>5.006767765384884</v>
       </c>
       <c r="E26">
-        <v>1.046706449125523</v>
+        <v>1.11253925900545</v>
       </c>
       <c r="F26">
-        <v>1.579987437118256</v>
+        <v>1.645820246998183</v>
       </c>
       <c r="G26">
         <v>1.77</v>
@@ -3413,28 +3413,28 @@
         <v>0.497</v>
       </c>
       <c r="M26">
-        <v>0.08737330527263953</v>
+        <v>0.09101385965899952</v>
       </c>
       <c r="N26">
-        <v>0.4096266947273605</v>
+        <v>0.4059861403410004</v>
       </c>
       <c r="O26">
-        <v>0.110025730203769</v>
+        <v>0.1090478772955927</v>
       </c>
       <c r="P26">
-        <v>0.2996009645235914</v>
+        <v>0.2969382630454077</v>
       </c>
       <c r="Q26">
-        <v>0.3796009645235914</v>
+        <v>0.3769382630454077</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08234087566529204</v>
+        <v>0.08272177668832903</v>
       </c>
       <c r="T26">
-        <v>0.7122496802126512</v>
+        <v>0.7196741501223435</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.688236223285384</v>
+        <v>5.460706774353968</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07215293751624677</v>
+        <v>0.07201966872687159</v>
       </c>
       <c r="C27">
-        <v>5.130947518386701</v>
+        <v>5.074880128623644</v>
       </c>
       <c r="D27">
-        <v>5.006767765384884</v>
+        <v>5.016533185501755</v>
       </c>
       <c r="E27">
-        <v>1.11253925900545</v>
+        <v>1.178372068885378</v>
       </c>
       <c r="F27">
-        <v>1.645820246998183</v>
+        <v>1.711653056878111</v>
       </c>
       <c r="G27">
         <v>1.77</v>
@@ -3495,28 +3495,28 @@
         <v>0.497</v>
       </c>
       <c r="M27">
-        <v>0.09101385965899952</v>
+        <v>0.09465441404535951</v>
       </c>
       <c r="N27">
-        <v>0.4059861403410004</v>
+        <v>0.4023455859546405</v>
       </c>
       <c r="O27">
-        <v>0.1090478772955927</v>
+        <v>0.1080700243874164</v>
       </c>
       <c r="P27">
-        <v>0.2969382630454077</v>
+        <v>0.2942755615672241</v>
       </c>
       <c r="Q27">
-        <v>0.3769382630454077</v>
+        <v>0.374275561567224</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08272177668832903</v>
+        <v>0.08311297233361026</v>
       </c>
       <c r="T27">
-        <v>0.7196741501223435</v>
+        <v>0.7272992813809462</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.460706774353968</v>
+        <v>5.250679590724968</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07201966872687159</v>
+        <v>0.0718863999374964</v>
       </c>
       <c r="C28">
-        <v>5.074880128623644</v>
+        <v>5.018850907115661</v>
       </c>
       <c r="D28">
-        <v>5.016533185501755</v>
+        <v>5.026336773873699</v>
       </c>
       <c r="E28">
-        <v>1.178372068885378</v>
+        <v>1.244204878765305</v>
       </c>
       <c r="F28">
-        <v>1.711653056878111</v>
+        <v>1.777485866758038</v>
       </c>
       <c r="G28">
         <v>1.77</v>
@@ -3577,28 +3577,28 @@
         <v>0.497</v>
       </c>
       <c r="M28">
-        <v>0.09465441404535951</v>
+        <v>0.09829496843171949</v>
       </c>
       <c r="N28">
-        <v>0.4023455859546405</v>
+        <v>0.3987050315682805</v>
       </c>
       <c r="O28">
-        <v>0.1080700243874164</v>
+        <v>0.1070921714792401</v>
       </c>
       <c r="P28">
-        <v>0.2942755615672241</v>
+        <v>0.2916128600890404</v>
       </c>
       <c r="Q28">
-        <v>0.374275561567224</v>
+        <v>0.3716128600890403</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08311297233361026</v>
+        <v>0.0835148856678033</v>
       </c>
       <c r="T28">
-        <v>0.7272992813809462</v>
+        <v>0.7351333203452641</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.250679590724968</v>
+        <v>5.056209976253673</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0718863999374964</v>
+        <v>0.07175313114812121</v>
       </c>
       <c r="C29">
-        <v>5.018850907115661</v>
+        <v>4.962860078072502</v>
       </c>
       <c r="D29">
-        <v>5.026336773873699</v>
+        <v>5.036178754710467</v>
       </c>
       <c r="E29">
-        <v>1.244204878765305</v>
+        <v>1.310037688645233</v>
       </c>
       <c r="F29">
-        <v>1.777485866758038</v>
+        <v>1.843318676637965</v>
       </c>
       <c r="G29">
         <v>1.77</v>
@@ -3659,28 +3659,28 @@
         <v>0.497</v>
       </c>
       <c r="M29">
-        <v>0.09829496843171949</v>
+        <v>0.1019355228180795</v>
       </c>
       <c r="N29">
-        <v>0.3987050315682805</v>
+        <v>0.3950644771819205</v>
       </c>
       <c r="O29">
-        <v>0.1070921714792401</v>
+        <v>0.1061143185710638</v>
       </c>
       <c r="P29">
-        <v>0.2916128600890404</v>
+        <v>0.2889501586108567</v>
       </c>
       <c r="Q29">
-        <v>0.3716128600890403</v>
+        <v>0.3689501586108566</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0835148856678033</v>
+        <v>0.08392796326127946</v>
       </c>
       <c r="T29">
-        <v>0.7351333203452641</v>
+        <v>0.7431849715030353</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.056209976253673</v>
+        <v>4.875631048530328</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07175313114812121</v>
+        <v>0.07161986235874604</v>
       </c>
       <c r="C30">
-        <v>4.962860078072502</v>
+        <v>4.90690786746344</v>
       </c>
       <c r="D30">
-        <v>5.036178754710467</v>
+        <v>5.046059353981333</v>
       </c>
       <c r="E30">
-        <v>1.310037688645233</v>
+        <v>1.37587049852516</v>
       </c>
       <c r="F30">
-        <v>1.843318676637965</v>
+        <v>1.909151486517893</v>
       </c>
       <c r="G30">
         <v>1.77</v>
@@ -3741,28 +3741,28 @@
         <v>0.497</v>
       </c>
       <c r="M30">
-        <v>0.1019355228180795</v>
+        <v>0.1055760772044395</v>
       </c>
       <c r="N30">
-        <v>0.3950644771819205</v>
+        <v>0.3914239227955605</v>
       </c>
       <c r="O30">
-        <v>0.1061143185710638</v>
+        <v>0.1051364656628876</v>
       </c>
       <c r="P30">
-        <v>0.2889501586108567</v>
+        <v>0.286287457132673</v>
       </c>
       <c r="Q30">
-        <v>0.3689501586108566</v>
+        <v>0.366287457132673</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08392796326127946</v>
+        <v>0.08435267684330428</v>
       </c>
       <c r="T30">
-        <v>0.7431849715030353</v>
+        <v>0.7514634297356733</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.875631048530328</v>
+        <v>4.707505839960316</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07161986235874604</v>
+        <v>0.07148659356937086</v>
       </c>
       <c r="C31">
-        <v>4.90690786746344</v>
+        <v>4.850994503034585</v>
       </c>
       <c r="D31">
-        <v>5.046059353981333</v>
+        <v>5.055978799432404</v>
       </c>
       <c r="E31">
-        <v>1.37587049852516</v>
+        <v>1.441703308405087</v>
       </c>
       <c r="F31">
-        <v>1.909151486517892</v>
+        <v>1.97498429639782</v>
       </c>
       <c r="G31">
         <v>1.77</v>
@@ -3823,28 +3823,28 @@
         <v>0.497</v>
       </c>
       <c r="M31">
-        <v>0.1055760772044394</v>
+        <v>0.1092166315907994</v>
       </c>
       <c r="N31">
-        <v>0.3914239227955605</v>
+        <v>0.3877833684092006</v>
       </c>
       <c r="O31">
-        <v>0.1051364656628876</v>
+        <v>0.1041586127547113</v>
       </c>
       <c r="P31">
-        <v>0.286287457132673</v>
+        <v>0.2836247556544893</v>
       </c>
       <c r="Q31">
-        <v>0.366287457132673</v>
+        <v>0.3636247556544893</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08435267684330428</v>
+        <v>0.08478952509910123</v>
       </c>
       <c r="T31">
-        <v>0.7514634297356733</v>
+        <v>0.7599784153463867</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.707505839960318</v>
+        <v>4.550588978628307</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07148659356937086</v>
+        <v>0.07192015977999568</v>
       </c>
       <c r="C32">
-        <v>4.850994503034585</v>
+        <v>4.753032586336093</v>
       </c>
       <c r="D32">
-        <v>5.055978799432404</v>
+        <v>5.023849692613839</v>
       </c>
       <c r="E32">
-        <v>1.441703308405087</v>
+        <v>1.507536118285015</v>
       </c>
       <c r="F32">
-        <v>1.97498429639782</v>
+        <v>2.040817106277747</v>
       </c>
       <c r="G32">
         <v>1.77</v>
@@ -3905,45 +3905,45 @@
         <v>0.497</v>
       </c>
       <c r="M32">
-        <v>0.1092166315907994</v>
+        <v>0.1179592287428538</v>
       </c>
       <c r="N32">
-        <v>0.3877833684092006</v>
+        <v>0.3790407712571462</v>
       </c>
       <c r="O32">
-        <v>0.1041586127547113</v>
+        <v>0.1018103511596695</v>
       </c>
       <c r="P32">
-        <v>0.2836247556544893</v>
+        <v>0.2772304200974767</v>
       </c>
       <c r="Q32">
-        <v>0.3636247556544893</v>
+        <v>0.3572304200974767</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08478952509910123</v>
+        <v>0.08523903562318214</v>
       </c>
       <c r="T32">
-        <v>0.7599784153463867</v>
+        <v>0.7687402121342222</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.2686</v>
       </c>
       <c r="W32">
-        <v>0.04044642</v>
+        <v>0.04227492000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.550588978628307</v>
+        <v>4.213320189499028</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07192015977999568</v>
+        <v>0.07180517599062049</v>
       </c>
       <c r="C33">
-        <v>4.753032586336093</v>
+        <v>4.695680712017439</v>
       </c>
       <c r="D33">
-        <v>5.023849692613839</v>
+        <v>5.032330628175114</v>
       </c>
       <c r="E33">
-        <v>1.507536118285015</v>
+        <v>1.573368928164942</v>
       </c>
       <c r="F33">
-        <v>2.040817106277747</v>
+        <v>2.106649916157674</v>
       </c>
       <c r="G33">
         <v>1.77</v>
@@ -3987,28 +3987,28 @@
         <v>0.497</v>
       </c>
       <c r="M33">
-        <v>0.1179592287428538</v>
+        <v>0.1217643651539136</v>
       </c>
       <c r="N33">
-        <v>0.3790407712571462</v>
+        <v>0.3752356348460864</v>
       </c>
       <c r="O33">
-        <v>0.1018103511596695</v>
+        <v>0.1007882915196588</v>
       </c>
       <c r="P33">
-        <v>0.2772304200974767</v>
+        <v>0.2744473433264276</v>
       </c>
       <c r="Q33">
-        <v>0.3572304200974767</v>
+        <v>0.3544473433264276</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08523903562318214</v>
+        <v>0.08570176704503013</v>
       </c>
       <c r="T33">
-        <v>0.7687402121342222</v>
+        <v>0.7777597088275822</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.213320189499028</v>
+        <v>4.081653933577185</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07180517599062049</v>
+        <v>0.07253495920124531</v>
       </c>
       <c r="C34">
-        <v>4.695680712017439</v>
+        <v>4.576501500884508</v>
       </c>
       <c r="D34">
-        <v>5.032330628175114</v>
+        <v>4.978984226922109</v>
       </c>
       <c r="E34">
-        <v>1.573368928164942</v>
+        <v>1.639201738044869</v>
       </c>
       <c r="F34">
-        <v>2.106649916157674</v>
+        <v>2.172482726037602</v>
       </c>
       <c r="G34">
         <v>1.77</v>
@@ -4069,45 +4069,45 @@
         <v>0.497</v>
       </c>
       <c r="M34">
-        <v>0.1217643651539136</v>
+        <v>0.133173191106105</v>
       </c>
       <c r="N34">
-        <v>0.3752356348460864</v>
+        <v>0.363826808893895</v>
       </c>
       <c r="O34">
-        <v>0.1007882915196588</v>
+        <v>0.0977238808689002</v>
       </c>
       <c r="P34">
-        <v>0.2744473433264276</v>
+        <v>0.2661029280249948</v>
       </c>
       <c r="Q34">
-        <v>0.3544473433264276</v>
+        <v>0.3461029280249948</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08570176704503013</v>
+        <v>0.08617831134514226</v>
       </c>
       <c r="T34">
-        <v>0.7777597088275822</v>
+        <v>0.7870484442282067</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.2686</v>
       </c>
       <c r="W34">
-        <v>0.04227492000000001</v>
+        <v>0.04483482</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.081653933577185</v>
+        <v>3.731982359753008</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07253495920124531</v>
+        <v>0.07244557441187012</v>
       </c>
       <c r="C35">
-        <v>4.576501500884508</v>
+        <v>4.51714176713619</v>
       </c>
       <c r="D35">
-        <v>4.978984226922109</v>
+        <v>4.985457303053719</v>
       </c>
       <c r="E35">
-        <v>1.639201738044869</v>
+        <v>1.705034547924797</v>
       </c>
       <c r="F35">
-        <v>2.172482726037602</v>
+        <v>2.238315535917529</v>
       </c>
       <c r="G35">
         <v>1.77</v>
@@ -4151,28 +4151,28 @@
         <v>0.497</v>
       </c>
       <c r="M35">
-        <v>0.133173191106105</v>
+        <v>0.1372087423517445</v>
       </c>
       <c r="N35">
-        <v>0.363826808893895</v>
+        <v>0.3597912576482555</v>
       </c>
       <c r="O35">
-        <v>0.0977238808689002</v>
+        <v>0.09663993180432143</v>
       </c>
       <c r="P35">
-        <v>0.2661029280249948</v>
+        <v>0.2631513258439341</v>
       </c>
       <c r="Q35">
-        <v>0.3461029280249948</v>
+        <v>0.343151325843934</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08617831134514226</v>
+        <v>0.08666929638162141</v>
       </c>
       <c r="T35">
-        <v>0.7870484442282067</v>
+        <v>0.7966186564591533</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.731982359753008</v>
+        <v>3.622218172701449</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07244557441187012</v>
+        <v>0.07235618962249493</v>
       </c>
       <c r="C36">
-        <v>4.51714176713619</v>
+        <v>4.457798886327298</v>
       </c>
       <c r="D36">
-        <v>4.985457303053719</v>
+        <v>4.991947232124755</v>
       </c>
       <c r="E36">
-        <v>1.705034547924797</v>
+        <v>1.770867357804724</v>
       </c>
       <c r="F36">
-        <v>2.238315535917529</v>
+        <v>2.304148345797457</v>
       </c>
       <c r="G36">
         <v>1.77</v>
@@ -4233,28 +4233,28 @@
         <v>0.497</v>
       </c>
       <c r="M36">
-        <v>0.1372087423517445</v>
+        <v>0.1412442935973841</v>
       </c>
       <c r="N36">
-        <v>0.3597912576482555</v>
+        <v>0.3557557064026159</v>
       </c>
       <c r="O36">
-        <v>0.09663993180432143</v>
+        <v>0.09555598273974263</v>
       </c>
       <c r="P36">
-        <v>0.2631513258439341</v>
+        <v>0.2601997236628733</v>
       </c>
       <c r="Q36">
-        <v>0.343151325843934</v>
+        <v>0.3401997236628732</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08666929638162141</v>
+        <v>0.08717538864999222</v>
       </c>
       <c r="T36">
-        <v>0.7966186564591533</v>
+        <v>0.8064833367587442</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.622218172701449</v>
+        <v>3.518726224909979</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07235618962249493</v>
+        <v>0.07300405603311977</v>
       </c>
       <c r="C37">
-        <v>4.457798886327298</v>
+        <v>4.345305695515077</v>
       </c>
       <c r="D37">
-        <v>4.991947232124755</v>
+        <v>4.945286851192461</v>
       </c>
       <c r="E37">
-        <v>1.770867357804724</v>
+        <v>1.836700167684651</v>
       </c>
       <c r="F37">
-        <v>2.304148345797457</v>
+        <v>2.369981155677384</v>
       </c>
       <c r="G37">
         <v>1.77</v>
@@ -4315,45 +4315,45 @@
         <v>0.497</v>
       </c>
       <c r="M37">
-        <v>0.1412442935973841</v>
+        <v>0.1519157920789203</v>
       </c>
       <c r="N37">
-        <v>0.3557557064026159</v>
+        <v>0.3450842079210796</v>
       </c>
       <c r="O37">
-        <v>0.09555598273974263</v>
+        <v>0.092689618247602</v>
       </c>
       <c r="P37">
-        <v>0.2601997236628733</v>
+        <v>0.2523945896734776</v>
       </c>
       <c r="Q37">
-        <v>0.3401997236628732</v>
+        <v>0.3323945896734776</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08717538864999222</v>
+        <v>0.08769729630174963</v>
       </c>
       <c r="T37">
-        <v>0.8064833367587442</v>
+        <v>0.8166562883176975</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.2686</v>
       </c>
       <c r="W37">
-        <v>0.04483482</v>
+        <v>0.04688274000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.518726224909979</v>
+        <v>3.271549278707036</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07300405603311977</v>
+        <v>0.07293515044374457</v>
       </c>
       <c r="C38">
-        <v>4.345305695515078</v>
+        <v>4.284394082443806</v>
       </c>
       <c r="D38">
-        <v>4.945286851192461</v>
+        <v>4.950208048001117</v>
       </c>
       <c r="E38">
-        <v>1.836700167684651</v>
+        <v>1.902532977564579</v>
       </c>
       <c r="F38">
-        <v>2.369981155677384</v>
+        <v>2.435813965557311</v>
       </c>
       <c r="G38">
         <v>1.77</v>
@@ -4397,28 +4397,28 @@
         <v>0.497</v>
       </c>
       <c r="M38">
-        <v>0.1519157920789203</v>
+        <v>0.1561356751922237</v>
       </c>
       <c r="N38">
-        <v>0.3450842079210797</v>
+        <v>0.3408643248077763</v>
       </c>
       <c r="O38">
-        <v>0.09268961824760201</v>
+        <v>0.09155615764336873</v>
       </c>
       <c r="P38">
-        <v>0.2523945896734777</v>
+        <v>0.2493081671644076</v>
       </c>
       <c r="Q38">
-        <v>0.3323945896734776</v>
+        <v>0.3293081671644076</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08769729630174963</v>
+        <v>0.08823577245038822</v>
       </c>
       <c r="T38">
-        <v>0.8166562883176974</v>
+        <v>0.827152190719792</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.271549278707037</v>
+        <v>3.183129027931171</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07293515044374457</v>
+        <v>0.07286624485436941</v>
       </c>
       <c r="C39">
-        <v>4.284394082443806</v>
+        <v>4.223492273577211</v>
       </c>
       <c r="D39">
-        <v>4.950208048001117</v>
+        <v>4.95513904901445</v>
       </c>
       <c r="E39">
-        <v>1.902532977564579</v>
+        <v>1.968365787444506</v>
       </c>
       <c r="F39">
-        <v>2.435813965557311</v>
+        <v>2.501646775437238</v>
       </c>
       <c r="G39">
         <v>1.77</v>
@@ -4479,28 +4479,28 @@
         <v>0.497</v>
       </c>
       <c r="M39">
-        <v>0.1561356751922237</v>
+        <v>0.160355558305527</v>
       </c>
       <c r="N39">
-        <v>0.3408643248077763</v>
+        <v>0.336644441694473</v>
       </c>
       <c r="O39">
-        <v>0.09155615764336873</v>
+        <v>0.09042269703913546</v>
       </c>
       <c r="P39">
-        <v>0.2493081671644076</v>
+        <v>0.2462217446553375</v>
       </c>
       <c r="Q39">
-        <v>0.3293081671644076</v>
+        <v>0.3262217446553375</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08823577245038822</v>
+        <v>0.08879161879736999</v>
       </c>
       <c r="T39">
-        <v>0.827152190719792</v>
+        <v>0.8379866706187283</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.183129027931171</v>
+        <v>3.099362474564562</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07286624485436941</v>
+        <v>0.07279733926499422</v>
       </c>
       <c r="C40">
-        <v>4.223492273577211</v>
+        <v>4.162600298243001</v>
       </c>
       <c r="D40">
-        <v>4.95513904901445</v>
+        <v>4.960079883560167</v>
       </c>
       <c r="E40">
-        <v>1.968365787444506</v>
+        <v>2.034198597324433</v>
       </c>
       <c r="F40">
-        <v>2.501646775437238</v>
+        <v>2.567479585317165</v>
       </c>
       <c r="G40">
         <v>1.77</v>
@@ -4561,28 +4561,28 @@
         <v>0.497</v>
       </c>
       <c r="M40">
-        <v>0.160355558305527</v>
+        <v>0.1645754414188303</v>
       </c>
       <c r="N40">
-        <v>0.336644441694473</v>
+        <v>0.3324245585811697</v>
       </c>
       <c r="O40">
-        <v>0.09042269703913546</v>
+        <v>0.08928923643490218</v>
       </c>
       <c r="P40">
-        <v>0.2462217446553375</v>
+        <v>0.2431353221462675</v>
       </c>
       <c r="Q40">
-        <v>0.3262217446553375</v>
+        <v>0.3231353221462675</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08879161879736999</v>
+        <v>0.08936568961474461</v>
       </c>
       <c r="T40">
-        <v>0.8379866706187283</v>
+        <v>0.8491763793668102</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.099362474564562</v>
+        <v>3.01989164188342</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07279733926499422</v>
+        <v>0.07501040167561904</v>
       </c>
       <c r="C41">
-        <v>4.162600298243001</v>
+        <v>3.94285200964207</v>
       </c>
       <c r="D41">
-        <v>4.960079883560167</v>
+        <v>4.806164404839164</v>
       </c>
       <c r="E41">
-        <v>2.034198597324433</v>
+        <v>2.10003140720436</v>
       </c>
       <c r="F41">
-        <v>2.567479585317165</v>
+        <v>2.633312395197093</v>
       </c>
       <c r="G41">
         <v>1.77</v>
@@ -4643,45 +4643,45 @@
         <v>0.497</v>
       </c>
       <c r="M41">
-        <v>0.1645754414188303</v>
+        <v>0.189335161214671</v>
       </c>
       <c r="N41">
-        <v>0.3324245585811697</v>
+        <v>0.307664838785329</v>
       </c>
       <c r="O41">
-        <v>0.08928923643490218</v>
+        <v>0.08263877569773938</v>
       </c>
       <c r="P41">
-        <v>0.2431353221462675</v>
+        <v>0.2250260630875897</v>
       </c>
       <c r="Q41">
-        <v>0.3231353221462675</v>
+        <v>0.3050260630875896</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08936568961474461</v>
+        <v>0.08995889612603172</v>
       </c>
       <c r="T41">
-        <v>0.8491763793668102</v>
+        <v>0.8607390784064948</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.2686</v>
       </c>
       <c r="W41">
-        <v>0.04688274000000001</v>
+        <v>0.05258766000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.01989164188342</v>
+        <v>2.624974657699708</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07501040167561904</v>
+        <v>0.07499854528624385</v>
       </c>
       <c r="C42">
-        <v>3.94285200964207</v>
+        <v>3.877818340456988</v>
       </c>
       <c r="D42">
-        <v>4.806164404839164</v>
+        <v>4.806963545534009</v>
       </c>
       <c r="E42">
-        <v>2.10003140720436</v>
+        <v>2.165864217084288</v>
       </c>
       <c r="F42">
-        <v>2.633312395197093</v>
+        <v>2.69914520507702</v>
       </c>
       <c r="G42">
         <v>1.77</v>
@@ -4725,28 +4725,28 @@
         <v>0.497</v>
       </c>
       <c r="M42">
-        <v>0.189335161214671</v>
+        <v>0.1940685402450378</v>
       </c>
       <c r="N42">
-        <v>0.307664838785329</v>
+        <v>0.3029314597549622</v>
       </c>
       <c r="O42">
-        <v>0.08263877569773938</v>
+        <v>0.08136739009018286</v>
       </c>
       <c r="P42">
-        <v>0.2250260630875897</v>
+        <v>0.2215640696647794</v>
       </c>
       <c r="Q42">
-        <v>0.3050260630875896</v>
+        <v>0.3015640696647793</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08995889612603172</v>
+        <v>0.0905722113326167</v>
       </c>
       <c r="T42">
-        <v>0.8607390784064948</v>
+        <v>0.8726937333458296</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.624974657699708</v>
+        <v>2.560950885560691</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07499854528624385</v>
+        <v>0.07618472209686868</v>
       </c>
       <c r="C43">
-        <v>3.877818340456988</v>
+        <v>3.733330339342774</v>
       </c>
       <c r="D43">
-        <v>4.806963545534009</v>
+        <v>4.728308354299721</v>
       </c>
       <c r="E43">
-        <v>2.165864217084288</v>
+        <v>2.231697026964215</v>
       </c>
       <c r="F43">
-        <v>2.69914520507702</v>
+        <v>2.764978014956948</v>
       </c>
       <c r="G43">
         <v>1.77</v>
@@ -4807,45 +4807,45 @@
         <v>0.497</v>
       </c>
       <c r="M43">
-        <v>0.1940685402450378</v>
+        <v>0.2095853335337367</v>
       </c>
       <c r="N43">
-        <v>0.3029314597549622</v>
+        <v>0.2874146664662633</v>
       </c>
       <c r="O43">
-        <v>0.08136739009018286</v>
+        <v>0.07719957941283834</v>
       </c>
       <c r="P43">
-        <v>0.2215640696647794</v>
+        <v>0.210215087053425</v>
       </c>
       <c r="Q43">
-        <v>0.3015640696647793</v>
+        <v>0.290215087053425</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0905722113326167</v>
+        <v>0.09120667533942875</v>
       </c>
       <c r="T43">
-        <v>0.8726937333458296</v>
+        <v>0.8850606177658312</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.2686</v>
       </c>
       <c r="W43">
-        <v>0.05258766000000001</v>
+        <v>0.05544012000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.560950885560691</v>
+        <v>2.371349137939553</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07618472209686869</v>
+        <v>0.0762013903074935</v>
       </c>
       <c r="C44">
-        <v>3.733330339342773</v>
+        <v>3.666410598255667</v>
       </c>
       <c r="D44">
-        <v>4.72830835429972</v>
+        <v>4.727221423092542</v>
       </c>
       <c r="E44">
-        <v>2.231697026964215</v>
+        <v>2.297529836844142</v>
       </c>
       <c r="F44">
-        <v>2.764978014956947</v>
+        <v>2.830810824836875</v>
       </c>
       <c r="G44">
         <v>1.77</v>
@@ -4889,28 +4889,28 @@
         <v>0.497</v>
       </c>
       <c r="M44">
-        <v>0.2095853335337366</v>
+        <v>0.2145754605226351</v>
       </c>
       <c r="N44">
-        <v>0.2874146664662633</v>
+        <v>0.2824245394773649</v>
       </c>
       <c r="O44">
-        <v>0.07719957941283834</v>
+        <v>0.07585923130362021</v>
       </c>
       <c r="P44">
-        <v>0.210215087053425</v>
+        <v>0.2065653081737447</v>
       </c>
       <c r="Q44">
-        <v>0.290215087053425</v>
+        <v>0.2865653081737446</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09120667533942875</v>
+        <v>0.09186340124121664</v>
       </c>
       <c r="T44">
-        <v>0.8850606177658312</v>
+        <v>0.8978614279549556</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.371349137939553</v>
+        <v>2.316201483568865</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0762013903074935</v>
+        <v>0.0762180585181183</v>
       </c>
       <c r="C45">
-        <v>3.666410598255667</v>
+        <v>3.599491356775542</v>
       </c>
       <c r="D45">
-        <v>4.727221423092542</v>
+        <v>4.726134991492344</v>
       </c>
       <c r="E45">
-        <v>2.297529836844142</v>
+        <v>2.36336264672407</v>
       </c>
       <c r="F45">
-        <v>2.830810824836875</v>
+        <v>2.896643634716802</v>
       </c>
       <c r="G45">
         <v>1.77</v>
@@ -4971,28 +4971,28 @@
         <v>0.497</v>
       </c>
       <c r="M45">
-        <v>0.2145754605226351</v>
+        <v>0.2195655875115336</v>
       </c>
       <c r="N45">
-        <v>0.2824245394773649</v>
+        <v>0.2774344124884663</v>
       </c>
       <c r="O45">
-        <v>0.07585923130362021</v>
+        <v>0.07451888319440206</v>
       </c>
       <c r="P45">
-        <v>0.2065653081737447</v>
+        <v>0.2029155292940643</v>
       </c>
       <c r="Q45">
-        <v>0.2865653081737446</v>
+        <v>0.2829155292940643</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09186340124121664</v>
+        <v>0.09254358163949697</v>
       </c>
       <c r="T45">
-        <v>0.8978614279549556</v>
+        <v>0.9111194099365487</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.316201483568865</v>
+        <v>2.263560540760482</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0762180585181183</v>
+        <v>0.07623472672874312</v>
       </c>
       <c r="C46">
-        <v>3.599491356775542</v>
+        <v>3.53257261455801</v>
       </c>
       <c r="D46">
-        <v>4.726134991492344</v>
+        <v>4.72504905915474</v>
       </c>
       <c r="E46">
-        <v>2.36336264672407</v>
+        <v>2.429195456603997</v>
       </c>
       <c r="F46">
-        <v>2.896643634716802</v>
+        <v>2.96247644459673</v>
       </c>
       <c r="G46">
         <v>1.77</v>
@@ -5053,28 +5053,28 @@
         <v>0.497</v>
       </c>
       <c r="M46">
-        <v>0.2195655875115336</v>
+        <v>0.2245557145004321</v>
       </c>
       <c r="N46">
-        <v>0.2774344124884663</v>
+        <v>0.2724442854995679</v>
       </c>
       <c r="O46">
-        <v>0.07451888319440206</v>
+        <v>0.07317853508518393</v>
       </c>
       <c r="P46">
-        <v>0.2029155292940643</v>
+        <v>0.199265750414384</v>
       </c>
       <c r="Q46">
-        <v>0.2829155292940643</v>
+        <v>0.279265750414384</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09254358163949697</v>
+        <v>0.09324849587044204</v>
       </c>
       <c r="T46">
-        <v>0.9111194099365487</v>
+        <v>0.9248595003538362</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.263560540760482</v>
+        <v>2.213259195410249</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07623472672874312</v>
+        <v>0.07625139493936794</v>
       </c>
       <c r="C47">
-        <v>3.53257261455801</v>
+        <v>3.465654371259001</v>
       </c>
       <c r="D47">
-        <v>4.72504905915474</v>
+        <v>4.723963625735658</v>
       </c>
       <c r="E47">
-        <v>2.429195456603997</v>
+        <v>2.495028266483924</v>
       </c>
       <c r="F47">
-        <v>2.96247644459673</v>
+        <v>3.028309254476657</v>
       </c>
       <c r="G47">
         <v>1.77</v>
@@ -5135,28 +5135,28 @@
         <v>0.497</v>
       </c>
       <c r="M47">
-        <v>0.2245557145004321</v>
+        <v>0.2295458414893306</v>
       </c>
       <c r="N47">
-        <v>0.2724442854995679</v>
+        <v>0.2674541585106694</v>
       </c>
       <c r="O47">
-        <v>0.07317853508518393</v>
+        <v>0.07183818697596581</v>
       </c>
       <c r="P47">
-        <v>0.199265750414384</v>
+        <v>0.1956159715347036</v>
       </c>
       <c r="Q47">
-        <v>0.279265750414384</v>
+        <v>0.2756159715347035</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09324849587044204</v>
+        <v>0.09397951803586656</v>
       </c>
       <c r="T47">
-        <v>0.9248595003538362</v>
+        <v>0.939108483008801</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.213259195410249</v>
+        <v>2.165144865075244</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07625139493936794</v>
+        <v>0.07626806314999277</v>
       </c>
       <c r="C48">
-        <v>3.465654371259001</v>
+        <v>3.398736626534763</v>
       </c>
       <c r="D48">
-        <v>4.723963625735658</v>
+        <v>4.722878690891346</v>
       </c>
       <c r="E48">
-        <v>2.495028266483924</v>
+        <v>2.560861076363852</v>
       </c>
       <c r="F48">
-        <v>3.028309254476657</v>
+        <v>3.094142064356584</v>
       </c>
       <c r="G48">
         <v>1.77</v>
@@ -5217,28 +5217,28 @@
         <v>0.497</v>
       </c>
       <c r="M48">
-        <v>0.2295458414893306</v>
+        <v>0.2345359684782291</v>
       </c>
       <c r="N48">
-        <v>0.2674541585106694</v>
+        <v>0.2624640315217709</v>
       </c>
       <c r="O48">
-        <v>0.07183818697596581</v>
+        <v>0.07049783886674767</v>
       </c>
       <c r="P48">
-        <v>0.1956159715347036</v>
+        <v>0.1919661926550232</v>
       </c>
       <c r="Q48">
-        <v>0.2756159715347035</v>
+        <v>0.2719661926550232</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09397951803586656</v>
+        <v>0.09473812594338257</v>
       </c>
       <c r="T48">
-        <v>0.939108483008801</v>
+        <v>0.9538951631224437</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.165144865075244</v>
+        <v>2.119077953052366</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07626806314999277</v>
+        <v>0.07628473136061759</v>
       </c>
       <c r="C49">
-        <v>3.398736626534763</v>
+        <v>3.331819380041854</v>
       </c>
       <c r="D49">
-        <v>4.722878690891346</v>
+        <v>4.721794254278366</v>
       </c>
       <c r="E49">
-        <v>2.560861076363852</v>
+        <v>2.626693886243779</v>
       </c>
       <c r="F49">
-        <v>3.094142064356584</v>
+        <v>3.159974874236512</v>
       </c>
       <c r="G49">
         <v>1.77</v>
@@ -5299,28 +5299,28 @@
         <v>0.497</v>
       </c>
       <c r="M49">
-        <v>0.2345359684782291</v>
+        <v>0.2395260954671276</v>
       </c>
       <c r="N49">
-        <v>0.2624640315217709</v>
+        <v>0.2574739045328724</v>
       </c>
       <c r="O49">
-        <v>0.07049783886674767</v>
+        <v>0.06915749075752953</v>
       </c>
       <c r="P49">
-        <v>0.1919661926550232</v>
+        <v>0.1883164137753429</v>
       </c>
       <c r="Q49">
-        <v>0.2719661926550232</v>
+        <v>0.2683164137753428</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09473812594338257</v>
+        <v>0.09552591107811073</v>
       </c>
       <c r="T49">
-        <v>0.9538951631224437</v>
+        <v>0.9692505617019957</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.119077953052366</v>
+        <v>2.074930495697108</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07628473136061759</v>
+        <v>0.07630139957124239</v>
       </c>
       <c r="C50">
-        <v>3.331819380041855</v>
+        <v>3.264902631437155</v>
       </c>
       <c r="D50">
-        <v>4.721794254278366</v>
+        <v>4.720710315553594</v>
       </c>
       <c r="E50">
-        <v>2.626693886243779</v>
+        <v>2.692526696123706</v>
       </c>
       <c r="F50">
-        <v>3.159974874236511</v>
+        <v>3.225807684116439</v>
       </c>
       <c r="G50">
         <v>1.77</v>
@@ -5381,28 +5381,28 @@
         <v>0.497</v>
       </c>
       <c r="M50">
-        <v>0.2395260954671276</v>
+        <v>0.2445162224560261</v>
       </c>
       <c r="N50">
-        <v>0.2574739045328724</v>
+        <v>0.2524837775439739</v>
       </c>
       <c r="O50">
-        <v>0.06915749075752954</v>
+        <v>0.06781714264831139</v>
       </c>
       <c r="P50">
-        <v>0.1883164137753429</v>
+        <v>0.1846666348956625</v>
       </c>
       <c r="Q50">
-        <v>0.2683164137753429</v>
+        <v>0.2646666348956624</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09552591107811073</v>
+        <v>0.0963445897475341</v>
       </c>
       <c r="T50">
-        <v>0.9692505617019957</v>
+        <v>0.9852081327748635</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.074930495697109</v>
+        <v>2.032584975376759</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07630139957124239</v>
+        <v>0.08151100778186721</v>
       </c>
       <c r="C51">
-        <v>3.264902631437155</v>
+        <v>2.883039931008361</v>
       </c>
       <c r="D51">
-        <v>4.720710315553594</v>
+        <v>4.404680425004726</v>
       </c>
       <c r="E51">
-        <v>2.692526696123706</v>
+        <v>2.758359506003634</v>
       </c>
       <c r="F51">
-        <v>3.225807684116439</v>
+        <v>3.291640493996366</v>
       </c>
       <c r="G51">
         <v>1.77</v>
@@ -5463,45 +5463,45 @@
         <v>0.497</v>
       </c>
       <c r="M51">
-        <v>0.2445162224560261</v>
+        <v>0.2962476444596729</v>
       </c>
       <c r="N51">
-        <v>0.2524837775439739</v>
+        <v>0.2007523555403271</v>
       </c>
       <c r="O51">
-        <v>0.06781714264831139</v>
+        <v>0.05392208269813185</v>
       </c>
       <c r="P51">
-        <v>0.1846666348956625</v>
+        <v>0.1468302728421952</v>
       </c>
       <c r="Q51">
-        <v>0.2646666348956624</v>
+        <v>0.2268302728421952</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0963445897475341</v>
+        <v>0.09719601556373442</v>
       </c>
       <c r="T51">
-        <v>0.9852081327748635</v>
+        <v>1.001804006690646</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.2686</v>
       </c>
       <c r="W51">
-        <v>0.05544012000000001</v>
+        <v>0.065826</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.032584975376759</v>
+        <v>1.677650470120969</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08151100778186721</v>
+        <v>0.08163153479249202</v>
       </c>
       <c r="C52">
-        <v>2.883039931008361</v>
+        <v>2.810395626578067</v>
       </c>
       <c r="D52">
-        <v>4.404680425004726</v>
+        <v>4.397868930454361</v>
       </c>
       <c r="E52">
-        <v>2.758359506003634</v>
+        <v>2.824192315883561</v>
       </c>
       <c r="F52">
-        <v>3.291640493996366</v>
+        <v>3.357473303876294</v>
       </c>
       <c r="G52">
         <v>1.77</v>
@@ -5545,28 +5545,28 @@
         <v>0.497</v>
       </c>
       <c r="M52">
-        <v>0.2962476444596729</v>
+        <v>0.3021725973488664</v>
       </c>
       <c r="N52">
-        <v>0.2007523555403271</v>
+        <v>0.1948274026511336</v>
       </c>
       <c r="O52">
-        <v>0.05392208269813185</v>
+        <v>0.05233064035209448</v>
       </c>
       <c r="P52">
-        <v>0.1468302728421952</v>
+        <v>0.1424967622990391</v>
       </c>
       <c r="Q52">
-        <v>0.2268302728421952</v>
+        <v>0.2224967622990391</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09719601556373442</v>
+        <v>0.09808219345406537</v>
       </c>
       <c r="T52">
-        <v>1.001804006690646</v>
+        <v>1.019077263215236</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.677650470120969</v>
+        <v>1.644755362863695</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08163153479249202</v>
+        <v>0.08175206180311685</v>
       </c>
       <c r="C53">
-        <v>2.810395626578067</v>
+        <v>2.737772356509326</v>
       </c>
       <c r="D53">
-        <v>4.397868930454361</v>
+        <v>4.391078470265548</v>
       </c>
       <c r="E53">
-        <v>2.824192315883561</v>
+        <v>2.890025125763489</v>
       </c>
       <c r="F53">
-        <v>3.357473303876294</v>
+        <v>3.423306113756221</v>
       </c>
       <c r="G53">
         <v>1.77</v>
@@ -5627,28 +5627,28 @@
         <v>0.497</v>
       </c>
       <c r="M53">
-        <v>0.3021725973488664</v>
+        <v>0.3080975502380599</v>
       </c>
       <c r="N53">
-        <v>0.1948274026511336</v>
+        <v>0.1889024497619401</v>
       </c>
       <c r="O53">
-        <v>0.05233064035209448</v>
+        <v>0.05073919800605711</v>
       </c>
       <c r="P53">
-        <v>0.1424967622990391</v>
+        <v>0.138163251755883</v>
       </c>
       <c r="Q53">
-        <v>0.2224967622990391</v>
+        <v>0.2181632517558829</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09808219345406537</v>
+        <v>0.09900529542316011</v>
       </c>
       <c r="T53">
-        <v>1.019077263215236</v>
+        <v>1.037070238761684</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.644755362863695</v>
+        <v>1.613125452039393</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08175206180311685</v>
+        <v>0.08187258881374165</v>
       </c>
       <c r="C54">
-        <v>2.737772356509326</v>
+        <v>2.665170023519026</v>
       </c>
       <c r="D54">
-        <v>4.391078470265548</v>
+        <v>4.384308947155174</v>
       </c>
       <c r="E54">
-        <v>2.890025125763489</v>
+        <v>2.955857935643416</v>
       </c>
       <c r="F54">
-        <v>3.423306113756221</v>
+        <v>3.489138923636148</v>
       </c>
       <c r="G54">
         <v>1.77</v>
@@ -5709,28 +5709,28 @@
         <v>0.497</v>
       </c>
       <c r="M54">
-        <v>0.3080975502380599</v>
+        <v>0.3140225031272533</v>
       </c>
       <c r="N54">
-        <v>0.1889024497619401</v>
+        <v>0.1829774968727467</v>
       </c>
       <c r="O54">
-        <v>0.05073919800605711</v>
+        <v>0.04914775566001976</v>
       </c>
       <c r="P54">
-        <v>0.138163251755883</v>
+        <v>0.1338297412127269</v>
       </c>
       <c r="Q54">
-        <v>0.2181632517558829</v>
+        <v>0.2138297412127269</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09900529542316011</v>
+        <v>0.09996767832710993</v>
       </c>
       <c r="T54">
-        <v>1.037070238761684</v>
+        <v>1.055828872842023</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.613125452039393</v>
+        <v>1.582689122755631</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08187258881374165</v>
+        <v>0.08199311582436647</v>
       </c>
       <c r="C55">
-        <v>2.665170023519026</v>
+        <v>2.592588530923028</v>
       </c>
       <c r="D55">
-        <v>4.384308947155174</v>
+        <v>4.377560264439104</v>
       </c>
       <c r="E55">
-        <v>2.955857935643416</v>
+        <v>3.021690745523343</v>
       </c>
       <c r="F55">
-        <v>3.489138923636148</v>
+        <v>3.554971733516076</v>
       </c>
       <c r="G55">
         <v>1.77</v>
@@ -5791,28 +5791,28 @@
         <v>0.497</v>
       </c>
       <c r="M55">
-        <v>0.3140225031272533</v>
+        <v>0.3199474560164468</v>
       </c>
       <c r="N55">
-        <v>0.1829774968727467</v>
+        <v>0.1770525439835532</v>
       </c>
       <c r="O55">
-        <v>0.04914775566001976</v>
+        <v>0.04755631331398238</v>
       </c>
       <c r="P55">
-        <v>0.1338297412127269</v>
+        <v>0.1294962306695708</v>
       </c>
       <c r="Q55">
-        <v>0.2138297412127269</v>
+        <v>0.2094962306695708</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09996767832710993</v>
+        <v>0.1009719039660141</v>
       </c>
       <c r="T55">
-        <v>1.055828872842023</v>
+        <v>1.075403099708464</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.582689122755631</v>
+        <v>1.553380064926823</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08199311582436647</v>
+        <v>0.08211364283499129</v>
       </c>
       <c r="C56">
-        <v>2.592588530923028</v>
+        <v>2.520027782631591</v>
       </c>
       <c r="D56">
-        <v>4.377560264439104</v>
+        <v>4.370832326027593</v>
       </c>
       <c r="E56">
-        <v>3.021690745523343</v>
+        <v>3.087523555403271</v>
       </c>
       <c r="F56">
-        <v>3.554971733516076</v>
+        <v>3.620804543396003</v>
       </c>
       <c r="G56">
         <v>1.77</v>
@@ -5873,28 +5873,28 @@
         <v>0.497</v>
       </c>
       <c r="M56">
-        <v>0.3199474560164468</v>
+        <v>0.3258724089056402</v>
       </c>
       <c r="N56">
-        <v>0.1770525439835532</v>
+        <v>0.1711275910943598</v>
       </c>
       <c r="O56">
-        <v>0.04755631331398238</v>
+        <v>0.04596487096794503</v>
       </c>
       <c r="P56">
-        <v>0.1294962306695708</v>
+        <v>0.1251627201264147</v>
       </c>
       <c r="Q56">
-        <v>0.2094962306695708</v>
+        <v>0.2051627201264147</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1009719039660141</v>
+        <v>0.1020207618555362</v>
       </c>
       <c r="T56">
-        <v>1.075403099708464</v>
+        <v>1.095847292213413</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.553380064926823</v>
+        <v>1.525136791019063</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08211364283499129</v>
+        <v>0.1076664982526583</v>
       </c>
       <c r="C57">
-        <v>2.520027782631591</v>
+        <v>1.380013085178401</v>
       </c>
       <c r="D57">
-        <v>4.370832326027593</v>
+        <v>3.296650438454332</v>
       </c>
       <c r="E57">
-        <v>3.087523555403271</v>
+        <v>3.153356365283198</v>
       </c>
       <c r="F57">
-        <v>3.620804543396003</v>
+        <v>3.68663735327593</v>
       </c>
       <c r="G57">
         <v>1.77</v>
@@ -5955,45 +5955,45 @@
         <v>0.497</v>
       </c>
       <c r="M57">
-        <v>0.3258724089056402</v>
+        <v>0.5411983634609067</v>
       </c>
       <c r="N57">
-        <v>0.1711275910943598</v>
+        <v>-0.04419836346090666</v>
       </c>
       <c r="O57">
-        <v>0.04596487096794503</v>
+        <v>-0.01187168042559953</v>
       </c>
       <c r="P57">
-        <v>0.1251627201264147</v>
+        <v>-0.03232668303530713</v>
       </c>
       <c r="Q57">
-        <v>0.2051627201264147</v>
+        <v>0.04767331696469283</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1020207618555362</v>
+        <v>0.1039460442841147</v>
       </c>
       <c r="T57">
-        <v>1.095847292213413</v>
+        <v>1.133374630272707</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2686</v>
+        <v>0.2466640866138593</v>
       </c>
       <c r="W57">
-        <v>0.065826</v>
+        <v>0.1105897120850855</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.525136791019063</v>
+        <v>0.9183324147947108</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1076664982526583</v>
+        <v>0.1086764982526583</v>
       </c>
       <c r="C58">
-        <v>1.380013085178401</v>
+        <v>1.282464877726692</v>
       </c>
       <c r="D58">
-        <v>3.296650438454332</v>
+        <v>3.264935040882549</v>
       </c>
       <c r="E58">
-        <v>3.153356365283198</v>
+        <v>3.219189175163125</v>
       </c>
       <c r="F58">
-        <v>3.68663735327593</v>
+        <v>3.752470163155858</v>
       </c>
       <c r="G58">
         <v>1.77</v>
@@ -6037,37 +6037,37 @@
         <v>0.497</v>
       </c>
       <c r="M58">
-        <v>0.5411983634609067</v>
+        <v>0.5508626199512799</v>
       </c>
       <c r="N58">
-        <v>-0.04419836346090666</v>
+        <v>-0.05386261995127994</v>
       </c>
       <c r="O58">
-        <v>-0.01187168042559953</v>
+        <v>-0.01446749971891379</v>
       </c>
       <c r="P58">
-        <v>-0.03232668303530713</v>
+        <v>-0.03939512023236615</v>
       </c>
       <c r="Q58">
-        <v>0.04767331696469283</v>
+        <v>0.04060487976763381</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1039460442841147</v>
+        <v>0.1052982778721173</v>
       </c>
       <c r="T58">
-        <v>1.133374630272707</v>
+        <v>1.159732179813933</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2466640866138593</v>
+        <v>0.2423366464978267</v>
       </c>
       <c r="W58">
-        <v>0.1105897120850855</v>
+        <v>0.111224980294119</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9183324147947108</v>
+        <v>0.9022213197983124</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1086764982526583</v>
+        <v>0.1096864982526583</v>
       </c>
       <c r="C59">
-        <v>1.282464877726692</v>
+        <v>1.185521090878179</v>
       </c>
       <c r="D59">
-        <v>3.264935040882549</v>
+        <v>3.233824063913965</v>
       </c>
       <c r="E59">
-        <v>3.219189175163125</v>
+        <v>3.285021985043053</v>
       </c>
       <c r="F59">
-        <v>3.752470163155858</v>
+        <v>3.818302973035785</v>
       </c>
       <c r="G59">
         <v>1.77</v>
@@ -6119,37 +6119,37 @@
         <v>0.497</v>
       </c>
       <c r="M59">
-        <v>0.5508626199512799</v>
+        <v>0.5605268764416533</v>
       </c>
       <c r="N59">
-        <v>-0.05386261995127994</v>
+        <v>-0.06352687644165333</v>
       </c>
       <c r="O59">
-        <v>-0.01446749971891379</v>
+        <v>-0.01706331901222809</v>
       </c>
       <c r="P59">
-        <v>-0.03939512023236615</v>
+        <v>-0.04646355742942525</v>
       </c>
       <c r="Q59">
-        <v>0.04060487976763381</v>
+        <v>0.03353644257057471</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1052982778721173</v>
+        <v>0.1067149035357392</v>
       </c>
       <c r="T59">
-        <v>1.159732179813933</v>
+        <v>1.187344850761884</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2423366464978267</v>
+        <v>0.2381584284547607</v>
       </c>
       <c r="W59">
-        <v>0.111224980294119</v>
+        <v>0.1118383427028411</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9022213197983124</v>
+        <v>0.8866657798017897</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1096864982526583</v>
+        <v>0.1106964982526583</v>
       </c>
       <c r="C60">
-        <v>1.18552109087818</v>
+        <v>1.089164609475465</v>
       </c>
       <c r="D60">
-        <v>3.233824063913965</v>
+        <v>3.203300392391176</v>
       </c>
       <c r="E60">
-        <v>3.285021985043052</v>
+        <v>3.350854794922979</v>
       </c>
       <c r="F60">
-        <v>3.818302973035784</v>
+        <v>3.884135782915712</v>
       </c>
       <c r="G60">
         <v>1.77</v>
@@ -6201,37 +6201,37 @@
         <v>0.497</v>
       </c>
       <c r="M60">
-        <v>0.5605268764416532</v>
+        <v>0.5701911329320266</v>
       </c>
       <c r="N60">
-        <v>-0.06352687644165322</v>
+        <v>-0.07319113293202661</v>
       </c>
       <c r="O60">
-        <v>-0.01706331901222806</v>
+        <v>-0.01965913830554235</v>
       </c>
       <c r="P60">
-        <v>-0.04646355742942516</v>
+        <v>-0.05353199462648427</v>
       </c>
       <c r="Q60">
-        <v>0.0335364425705748</v>
+        <v>0.02646800537351569</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1067149035357391</v>
+        <v>0.1082006328902694</v>
       </c>
       <c r="T60">
-        <v>1.187344850761883</v>
+        <v>1.216304481268271</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2381584284547608</v>
+        <v>0.2341218449216292</v>
       </c>
       <c r="W60">
-        <v>0.1118383427028411</v>
+        <v>0.1124309131655048</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.88666577980179</v>
+        <v>0.8716375462458272</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1106964982526583</v>
+        <v>0.1117064982526583</v>
       </c>
       <c r="C61">
-        <v>1.089164609475465</v>
+        <v>0.9933789585103989</v>
       </c>
       <c r="D61">
-        <v>3.203300392391176</v>
+        <v>3.173347551306038</v>
       </c>
       <c r="E61">
-        <v>3.350854794922979</v>
+        <v>3.416687604802907</v>
       </c>
       <c r="F61">
-        <v>3.884135782915712</v>
+        <v>3.949968592795639</v>
       </c>
       <c r="G61">
         <v>1.77</v>
@@ -6283,37 +6283,37 @@
         <v>0.497</v>
       </c>
       <c r="M61">
-        <v>0.5701911329320266</v>
+        <v>0.5798553894223999</v>
       </c>
       <c r="N61">
-        <v>-0.07319113293202661</v>
+        <v>-0.08285538942239989</v>
       </c>
       <c r="O61">
-        <v>-0.01965913830554235</v>
+        <v>-0.02225495759885661</v>
       </c>
       <c r="P61">
-        <v>-0.05353199462648427</v>
+        <v>-0.06060043182354329</v>
       </c>
       <c r="Q61">
-        <v>0.02646800537351569</v>
+        <v>0.01939956817645667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1082006328902694</v>
+        <v>0.1097606487125261</v>
       </c>
       <c r="T61">
-        <v>1.216304481268271</v>
+        <v>1.246712093299977</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2341218449216292</v>
+        <v>0.2302198141729354</v>
       </c>
       <c r="W61">
-        <v>0.1124309131655048</v>
+        <v>0.1130037312794131</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8716375462458272</v>
+        <v>0.8571102538083969</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1117064982526583</v>
+        <v>0.1127164982526583</v>
       </c>
       <c r="C62">
-        <v>0.9933789585103989</v>
+        <v>0.8981482734723958</v>
       </c>
       <c r="D62">
-        <v>3.173347551306038</v>
+        <v>3.143949676147962</v>
       </c>
       <c r="E62">
-        <v>3.416687604802907</v>
+        <v>3.482520414682834</v>
       </c>
       <c r="F62">
-        <v>3.949968592795639</v>
+        <v>4.015801402675566</v>
       </c>
       <c r="G62">
         <v>1.77</v>
@@ -6365,37 +6365,37 @@
         <v>0.497</v>
       </c>
       <c r="M62">
-        <v>0.5798553894223999</v>
+        <v>0.5895196459127732</v>
       </c>
       <c r="N62">
-        <v>-0.08285538942239989</v>
+        <v>-0.09251964591277317</v>
       </c>
       <c r="O62">
-        <v>-0.02225495759885661</v>
+        <v>-0.02485077689217087</v>
       </c>
       <c r="P62">
-        <v>-0.06060043182354329</v>
+        <v>-0.0676688690206023</v>
       </c>
       <c r="Q62">
-        <v>0.01939956817645667</v>
+        <v>0.01233113097939766</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1097606487125261</v>
+        <v>0.1114006653461806</v>
       </c>
       <c r="T62">
-        <v>1.246712093299977</v>
+        <v>1.278679070051259</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2302198141729354</v>
+        <v>0.226445718858625</v>
       </c>
       <c r="W62">
-        <v>0.1130037312794131</v>
+        <v>0.1135577684715539</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8571102538083969</v>
+        <v>0.8430592660410462</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1127164982526583</v>
+        <v>0.1137264982526583</v>
       </c>
       <c r="C63">
-        <v>0.8981482734723958</v>
+        <v>0.8034572723297577</v>
       </c>
       <c r="D63">
-        <v>3.143949676147962</v>
+        <v>3.115091484885252</v>
       </c>
       <c r="E63">
-        <v>3.482520414682834</v>
+        <v>3.548353224562762</v>
       </c>
       <c r="F63">
-        <v>4.015801402675566</v>
+        <v>4.081634212555494</v>
       </c>
       <c r="G63">
         <v>1.77</v>
@@ -6447,37 +6447,37 @@
         <v>0.497</v>
       </c>
       <c r="M63">
-        <v>0.5895196459127732</v>
+        <v>0.5991839024031467</v>
       </c>
       <c r="N63">
-        <v>-0.09251964591277317</v>
+        <v>-0.1021839024031467</v>
       </c>
       <c r="O63">
-        <v>-0.02485077689217087</v>
+        <v>-0.0274465961854852</v>
       </c>
       <c r="P63">
-        <v>-0.0676688690206023</v>
+        <v>-0.07473730621766148</v>
       </c>
       <c r="Q63">
-        <v>0.01233113097939766</v>
+        <v>0.005262693782338485</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1114006653461806</v>
+        <v>0.1131269986447643</v>
       </c>
       <c r="T63">
-        <v>1.278679070051259</v>
+        <v>1.312328519263134</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.226445718858625</v>
+        <v>0.2227933685544536</v>
       </c>
       <c r="W63">
-        <v>0.1135577684715539</v>
+        <v>0.1140939334962062</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8430592660410462</v>
+        <v>0.8294615359436097</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1137264982526583</v>
+        <v>0.1147364982526583</v>
       </c>
       <c r="C64">
-        <v>0.8034572723297577</v>
+        <v>0.7092912290400735</v>
       </c>
       <c r="D64">
-        <v>3.115091484885252</v>
+        <v>3.086758251475495</v>
       </c>
       <c r="E64">
-        <v>3.548353224562762</v>
+        <v>3.614186034442689</v>
       </c>
       <c r="F64">
-        <v>4.081634212555494</v>
+        <v>4.147467022435421</v>
       </c>
       <c r="G64">
         <v>1.77</v>
@@ -6529,37 +6529,37 @@
         <v>0.497</v>
       </c>
       <c r="M64">
-        <v>0.5991839024031467</v>
+        <v>0.60884815889352</v>
       </c>
       <c r="N64">
-        <v>-0.1021839024031467</v>
+        <v>-0.11184815889352</v>
       </c>
       <c r="O64">
-        <v>-0.0274465961854852</v>
+        <v>-0.03004241547879946</v>
       </c>
       <c r="P64">
-        <v>-0.07473730621766148</v>
+        <v>-0.08180574341472049</v>
       </c>
       <c r="Q64">
-        <v>0.005262693782338485</v>
+        <v>-0.001805743414720534</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1131269986447643</v>
+        <v>0.114946647256785</v>
       </c>
       <c r="T64">
-        <v>1.312328519263134</v>
+        <v>1.347796857621597</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2227933685544536</v>
+        <v>0.2192569658789861</v>
       </c>
       <c r="W64">
-        <v>0.1140939334962062</v>
+        <v>0.1146130774089648</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8294615359436097</v>
+        <v>0.8162954798175208</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1147364982526583</v>
+        <v>0.1157464982526583</v>
       </c>
       <c r="C65">
-        <v>0.7092912290400735</v>
+        <v>0.6156359484931899</v>
       </c>
       <c r="D65">
-        <v>3.086758251475495</v>
+        <v>3.058935780808538</v>
       </c>
       <c r="E65">
-        <v>3.614186034442689</v>
+        <v>3.680018844322616</v>
       </c>
       <c r="F65">
-        <v>4.147467022435421</v>
+        <v>4.213299832315348</v>
       </c>
       <c r="G65">
         <v>1.77</v>
@@ -6611,37 +6611,37 @@
         <v>0.497</v>
       </c>
       <c r="M65">
-        <v>0.60884815889352</v>
+        <v>0.6185124153838932</v>
       </c>
       <c r="N65">
-        <v>-0.11184815889352</v>
+        <v>-0.1215124153838932</v>
       </c>
       <c r="O65">
-        <v>-0.03004241547879946</v>
+        <v>-0.03263823477211372</v>
       </c>
       <c r="P65">
-        <v>-0.08180574341472049</v>
+        <v>-0.08887418061177951</v>
       </c>
       <c r="Q65">
-        <v>-0.001805743414720534</v>
+        <v>-0.008874180611779553</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.114946647256785</v>
+        <v>0.1168673874583623</v>
       </c>
       <c r="T65">
-        <v>1.347796857621597</v>
+        <v>1.385235659222197</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2192569658789861</v>
+        <v>0.215831075787127</v>
       </c>
       <c r="W65">
-        <v>0.1146130774089648</v>
+        <v>0.1151159980744498</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8162954798175208</v>
+        <v>0.8035408629453721</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1157464982526583</v>
+        <v>0.1529591948629335</v>
       </c>
       <c r="C66">
-        <v>0.6156359484931899</v>
+        <v>-0.2127987541157585</v>
       </c>
       <c r="D66">
-        <v>3.058935780808538</v>
+        <v>2.296333888079518</v>
       </c>
       <c r="E66">
-        <v>3.680018844322616</v>
+        <v>3.745851654202544</v>
       </c>
       <c r="F66">
-        <v>4.213299832315348</v>
+        <v>4.279132642195276</v>
       </c>
       <c r="G66">
         <v>1.77</v>
@@ -6693,45 +6693,45 @@
         <v>0.497</v>
       </c>
       <c r="M66">
-        <v>0.6185124153838932</v>
+        <v>0.8592498345528115</v>
       </c>
       <c r="N66">
-        <v>-0.1215124153838932</v>
+        <v>-0.3622498345528115</v>
       </c>
       <c r="O66">
-        <v>-0.03263823477211372</v>
+        <v>-0.09730030556088516</v>
       </c>
       <c r="P66">
-        <v>-0.08887418061177951</v>
+        <v>-0.2649495289919263</v>
       </c>
       <c r="Q66">
-        <v>-0.008874180611779553</v>
+        <v>-0.1849495289919263</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1168673874583623</v>
+        <v>0.1220484459865304</v>
       </c>
       <c r="T66">
-        <v>1.385235659222197</v>
+        <v>1.486224133435359</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.215831075787127</v>
+        <v>0.1553613333768936</v>
       </c>
       <c r="W66">
-        <v>0.1151159980744498</v>
+        <v>0.1696034442579198</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8035408629453721</v>
+        <v>0.5784115166675114</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1529591948629335</v>
+        <v>0.1545091948629335</v>
       </c>
       <c r="C67">
-        <v>-0.2127987541157585</v>
+        <v>-0.3022318146197973</v>
       </c>
       <c r="D67">
-        <v>2.296333888079518</v>
+        <v>2.272733637455405</v>
       </c>
       <c r="E67">
-        <v>3.745851654202544</v>
+        <v>3.811684464082471</v>
       </c>
       <c r="F67">
-        <v>4.279132642195276</v>
+        <v>4.344965452075203</v>
       </c>
       <c r="G67">
         <v>1.77</v>
@@ -6775,37 +6775,37 @@
         <v>0.497</v>
       </c>
       <c r="M67">
-        <v>0.8592498345528115</v>
+        <v>0.8724690627767009</v>
       </c>
       <c r="N67">
-        <v>-0.3622498345528115</v>
+        <v>-0.3754690627767009</v>
       </c>
       <c r="O67">
-        <v>-0.09730030556088516</v>
+        <v>-0.1008509902618219</v>
       </c>
       <c r="P67">
-        <v>-0.2649495289919263</v>
+        <v>-0.274618072514879</v>
       </c>
       <c r="Q67">
-        <v>-0.1849495289919263</v>
+        <v>-0.1946180725148791</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1220484459865304</v>
+        <v>0.1242910473390754</v>
       </c>
       <c r="T67">
-        <v>1.486224133435359</v>
+        <v>1.529936607948164</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1553613333768936</v>
+        <v>0.153007373780274</v>
       </c>
       <c r="W67">
-        <v>0.1696034442579198</v>
+        <v>0.170076119344921</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5784115166675114</v>
+        <v>0.5696477058089129</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1545091948629335</v>
+        <v>0.1560591948629335</v>
       </c>
       <c r="C68">
-        <v>-0.3022318146197973</v>
+        <v>-0.3911847133638737</v>
       </c>
       <c r="D68">
-        <v>2.272733637455405</v>
+        <v>2.249613548591257</v>
       </c>
       <c r="E68">
-        <v>3.811684464082471</v>
+        <v>3.877517273962399</v>
       </c>
       <c r="F68">
-        <v>4.344965452075203</v>
+        <v>4.410798261955131</v>
       </c>
       <c r="G68">
         <v>1.77</v>
@@ -6857,37 +6857,37 @@
         <v>0.497</v>
       </c>
       <c r="M68">
-        <v>0.8724690627767009</v>
+        <v>0.8856882910005903</v>
       </c>
       <c r="N68">
-        <v>-0.3754690627767009</v>
+        <v>-0.3886882910005903</v>
       </c>
       <c r="O68">
-        <v>-0.1008509902618219</v>
+        <v>-0.1044016749627586</v>
       </c>
       <c r="P68">
-        <v>-0.274618072514879</v>
+        <v>-0.2842866160378318</v>
       </c>
       <c r="Q68">
-        <v>-0.1946180725148791</v>
+        <v>-0.2042866160378318</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1242910473390754</v>
+        <v>0.126669563925108</v>
       </c>
       <c r="T68">
-        <v>1.529936607948164</v>
+        <v>1.576298323340533</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.153007373780274</v>
+        <v>0.1507236816342997</v>
       </c>
       <c r="W68">
-        <v>0.170076119344921</v>
+        <v>0.1705346847278326</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5696477058089129</v>
+        <v>0.5611455012446007</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1560591948629335</v>
+        <v>0.1576091948629335</v>
       </c>
       <c r="C69">
-        <v>-0.3911847133638737</v>
+        <v>-0.4796719565629473</v>
       </c>
       <c r="D69">
-        <v>2.249613548591257</v>
+        <v>2.226959115272111</v>
       </c>
       <c r="E69">
-        <v>3.877517273962399</v>
+        <v>3.943350083842326</v>
       </c>
       <c r="F69">
-        <v>4.410798261955131</v>
+        <v>4.476631071835058</v>
       </c>
       <c r="G69">
         <v>1.77</v>
@@ -6939,37 +6939,37 @@
         <v>0.497</v>
       </c>
       <c r="M69">
-        <v>0.8856882910005903</v>
+        <v>0.8989075192244798</v>
       </c>
       <c r="N69">
-        <v>-0.3886882910005903</v>
+        <v>-0.4019075192244798</v>
       </c>
       <c r="O69">
-        <v>-0.1044016749627586</v>
+        <v>-0.1079523596636953</v>
       </c>
       <c r="P69">
-        <v>-0.2842866160378318</v>
+        <v>-0.2939551595607845</v>
       </c>
       <c r="Q69">
-        <v>-0.2042866160378318</v>
+        <v>-0.2139551595607845</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.126669563925108</v>
+        <v>0.1291967377977676</v>
       </c>
       <c r="T69">
-        <v>1.576298323340533</v>
+        <v>1.625557645944924</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1507236816342997</v>
+        <v>0.1485071569043836</v>
       </c>
       <c r="W69">
-        <v>0.1705346847278326</v>
+        <v>0.1709797628935998</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5611455012446007</v>
+        <v>0.5528933615204153</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1576091948629335</v>
+        <v>0.1591591948629335</v>
       </c>
       <c r="C70">
-        <v>-0.4796719565629473</v>
+        <v>-0.5677074719261355</v>
       </c>
       <c r="D70">
-        <v>2.226959115272111</v>
+        <v>2.204756409788851</v>
       </c>
       <c r="E70">
-        <v>3.943350083842326</v>
+        <v>4.009182893722254</v>
       </c>
       <c r="F70">
-        <v>4.476631071835058</v>
+        <v>4.542463881714986</v>
       </c>
       <c r="G70">
         <v>1.77</v>
@@ -7021,37 +7021,37 @@
         <v>0.497</v>
       </c>
       <c r="M70">
-        <v>0.8989075192244798</v>
+        <v>0.9121267474483692</v>
       </c>
       <c r="N70">
-        <v>-0.4019075192244798</v>
+        <v>-0.4151267474483692</v>
       </c>
       <c r="O70">
-        <v>-0.1079523596636953</v>
+        <v>-0.111503044364632</v>
       </c>
       <c r="P70">
-        <v>-0.2939551595607845</v>
+        <v>-0.3036237030837372</v>
       </c>
       <c r="Q70">
-        <v>-0.2139551595607845</v>
+        <v>-0.2236237030837372</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1291967377977676</v>
+        <v>0.1318869551460827</v>
       </c>
       <c r="T70">
-        <v>1.625557645944924</v>
+        <v>1.677994989362503</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1485071569043836</v>
+        <v>0.1463548792680882</v>
       </c>
       <c r="W70">
-        <v>0.1709797628935998</v>
+        <v>0.1714119402429679</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5528933615204153</v>
+        <v>0.5448804142520035</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1591591948629335</v>
+        <v>0.1607091948629335</v>
       </c>
       <c r="C71">
-        <v>-0.5677074719261355</v>
+        <v>-0.6553046372104379</v>
       </c>
       <c r="D71">
-        <v>2.204756409788851</v>
+        <v>2.182992054384475</v>
       </c>
       <c r="E71">
-        <v>4.009182893722254</v>
+        <v>4.075015703602181</v>
       </c>
       <c r="F71">
-        <v>4.542463881714986</v>
+        <v>4.608296691594913</v>
       </c>
       <c r="G71">
         <v>1.77</v>
@@ -7103,37 +7103,37 @@
         <v>0.497</v>
       </c>
       <c r="M71">
-        <v>0.9121267474483692</v>
+        <v>0.9253459756722586</v>
       </c>
       <c r="N71">
-        <v>-0.4151267474483692</v>
+        <v>-0.4283459756722586</v>
       </c>
       <c r="O71">
-        <v>-0.111503044364632</v>
+        <v>-0.1150537290655687</v>
       </c>
       <c r="P71">
-        <v>-0.3036237030837372</v>
+        <v>-0.31329224660669</v>
       </c>
       <c r="Q71">
-        <v>-0.2236237030837372</v>
+        <v>-0.23329224660669</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1318869551460827</v>
+        <v>0.1347565203176188</v>
       </c>
       <c r="T71">
-        <v>1.677994989362503</v>
+        <v>1.733928155674586</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1463548792680882</v>
+        <v>0.144264095278544</v>
       </c>
       <c r="W71">
-        <v>0.1714119402429679</v>
+        <v>0.1718317696680684</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5448804142520035</v>
+        <v>0.5370964083341178</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1607091948629335</v>
+        <v>0.1622591948629335</v>
       </c>
       <c r="C72">
-        <v>-0.6553046372104379</v>
+        <v>-0.7424763070997966</v>
       </c>
       <c r="D72">
-        <v>2.182992054384475</v>
+        <v>2.161653194375043</v>
       </c>
       <c r="E72">
-        <v>4.075015703602181</v>
+        <v>4.140848513482108</v>
       </c>
       <c r="F72">
-        <v>4.608296691594913</v>
+        <v>4.67412950147484</v>
       </c>
       <c r="G72">
         <v>1.77</v>
@@ -7185,37 +7185,37 @@
         <v>0.497</v>
       </c>
       <c r="M72">
-        <v>0.9253459756722586</v>
+        <v>0.9385652038961479</v>
       </c>
       <c r="N72">
-        <v>-0.4283459756722586</v>
+        <v>-0.441565203896148</v>
       </c>
       <c r="O72">
-        <v>-0.1150537290655687</v>
+        <v>-0.1186044137665053</v>
       </c>
       <c r="P72">
-        <v>-0.31329224660669</v>
+        <v>-0.3229607901296426</v>
       </c>
       <c r="Q72">
-        <v>-0.23329224660669</v>
+        <v>-0.2429607901296427</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1347565203176188</v>
+        <v>0.1378239865354677</v>
       </c>
       <c r="T72">
-        <v>1.733928155674586</v>
+        <v>1.793718781732331</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.144264095278544</v>
+        <v>0.142232206612649</v>
       </c>
       <c r="W72">
-        <v>0.1718317696680684</v>
+        <v>0.1722397729121801</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5370964083341178</v>
+        <v>0.5295316701885668</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1622591948629335</v>
+        <v>0.1638091948629335</v>
       </c>
       <c r="C73">
-        <v>-0.7424763070997966</v>
+        <v>-0.8292348385229396</v>
       </c>
       <c r="D73">
-        <v>2.161653194375043</v>
+        <v>2.140727472831828</v>
       </c>
       <c r="E73">
-        <v>4.140848513482108</v>
+        <v>4.206681323362035</v>
       </c>
       <c r="F73">
-        <v>4.67412950147484</v>
+        <v>4.739962311354767</v>
       </c>
       <c r="G73">
         <v>1.77</v>
@@ -7267,37 +7267,37 @@
         <v>0.497</v>
       </c>
       <c r="M73">
-        <v>0.9385652038961479</v>
+        <v>0.9517844321200373</v>
       </c>
       <c r="N73">
-        <v>-0.441565203896148</v>
+        <v>-0.4547844321200373</v>
       </c>
       <c r="O73">
-        <v>-0.1186044137665053</v>
+        <v>-0.122155098467442</v>
       </c>
       <c r="P73">
-        <v>-0.3229607901296426</v>
+        <v>-0.3326293336525953</v>
       </c>
       <c r="Q73">
-        <v>-0.2429607901296427</v>
+        <v>-0.2526293336525953</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1378239865354677</v>
+        <v>0.141110557483163</v>
       </c>
       <c r="T73">
-        <v>1.79371878173233</v>
+        <v>1.857780166794199</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.142232206612649</v>
+        <v>0.1402567592985845</v>
       </c>
       <c r="W73">
-        <v>0.1722397729121801</v>
+        <v>0.1726364427328442</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5295316701885668</v>
+        <v>0.5221770636581702</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1638091948629335</v>
+        <v>0.1653591948629335</v>
       </c>
       <c r="C74">
-        <v>-0.8292348385229396</v>
+        <v>-0.9155921145148027</v>
       </c>
       <c r="D74">
-        <v>2.140727472831828</v>
+        <v>2.120203006719891</v>
       </c>
       <c r="E74">
-        <v>4.206681323362035</v>
+        <v>4.272514133241962</v>
       </c>
       <c r="F74">
-        <v>4.739962311354767</v>
+        <v>4.805795121234694</v>
       </c>
       <c r="G74">
         <v>1.77</v>
@@ -7349,37 +7349,37 @@
         <v>0.497</v>
       </c>
       <c r="M74">
-        <v>0.9517844321200373</v>
+        <v>0.9650036603439266</v>
       </c>
       <c r="N74">
-        <v>-0.4547844321200373</v>
+        <v>-0.4680036603439266</v>
       </c>
       <c r="O74">
-        <v>-0.122155098467442</v>
+        <v>-0.1257057831683787</v>
       </c>
       <c r="P74">
-        <v>-0.3326293336525953</v>
+        <v>-0.3422978771755479</v>
       </c>
       <c r="Q74">
-        <v>-0.2526293336525953</v>
+        <v>-0.262297877175548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.141110557483163</v>
+        <v>0.1446405781306875</v>
       </c>
       <c r="T74">
-        <v>1.857780166794199</v>
+        <v>1.926586839638428</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1402567592985845</v>
+        <v>0.1383354338287409</v>
       </c>
       <c r="W74">
-        <v>0.1726364427328442</v>
+        <v>0.1730222448871888</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5221770636581702</v>
+        <v>0.5150239531970993</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1653591948629335</v>
+        <v>0.1669091948629335</v>
       </c>
       <c r="C75">
-        <v>-0.9155921145148027</v>
+        <v>-1.001559566718344</v>
       </c>
       <c r="D75">
-        <v>2.120203006719891</v>
+        <v>2.100068364396278</v>
       </c>
       <c r="E75">
-        <v>4.272514133241962</v>
+        <v>4.33834694312189</v>
       </c>
       <c r="F75">
-        <v>4.805795121234694</v>
+        <v>4.871627931114622</v>
       </c>
       <c r="G75">
         <v>1.77</v>
@@ -7431,37 +7431,37 @@
         <v>0.497</v>
       </c>
       <c r="M75">
-        <v>0.9650036603439266</v>
+        <v>0.9782228885678161</v>
       </c>
       <c r="N75">
-        <v>-0.4680036603439266</v>
+        <v>-0.4812228885678161</v>
       </c>
       <c r="O75">
-        <v>-0.1257057831683787</v>
+        <v>-0.1292564678693154</v>
       </c>
       <c r="P75">
-        <v>-0.3422978771755479</v>
+        <v>-0.3519664206985007</v>
       </c>
       <c r="Q75">
-        <v>-0.262297877175548</v>
+        <v>-0.2719664206985007</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1446405781306875</v>
+        <v>0.1484421388280217</v>
       </c>
       <c r="T75">
-        <v>1.926586839638428</v>
+        <v>2.000686333470676</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1383354338287409</v>
+        <v>0.1364660360742984</v>
       </c>
       <c r="W75">
-        <v>0.1730222448871888</v>
+        <v>0.1733976199562809</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5150239531970993</v>
+        <v>0.5080641700457871</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1669091948629335</v>
+        <v>0.1684591948629335</v>
       </c>
       <c r="C76">
-        <v>-1.001559566718344</v>
+        <v>-1.087148196616272</v>
       </c>
       <c r="D76">
-        <v>2.100068364396278</v>
+        <v>2.080312544378277</v>
       </c>
       <c r="E76">
-        <v>4.33834694312189</v>
+        <v>4.404179753001817</v>
       </c>
       <c r="F76">
-        <v>4.871627931114622</v>
+        <v>4.937460740994549</v>
       </c>
       <c r="G76">
         <v>1.77</v>
@@ -7513,37 +7513,37 @@
         <v>0.497</v>
       </c>
       <c r="M76">
-        <v>0.9782228885678161</v>
+        <v>0.9914421167917055</v>
       </c>
       <c r="N76">
-        <v>-0.4812228885678161</v>
+        <v>-0.4944421167917055</v>
       </c>
       <c r="O76">
-        <v>-0.1292564678693154</v>
+        <v>-0.1328071525702521</v>
       </c>
       <c r="P76">
-        <v>-0.3519664206985007</v>
+        <v>-0.3616349642214534</v>
       </c>
       <c r="Q76">
-        <v>-0.2719664206985007</v>
+        <v>-0.2816349642214534</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1484421388280217</v>
+        <v>0.1525478243811425</v>
       </c>
       <c r="T76">
-        <v>2.000686333470676</v>
+        <v>2.080713786809503</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1364660360742984</v>
+        <v>0.1346464889266411</v>
       </c>
       <c r="W76">
-        <v>0.1733976199562809</v>
+        <v>0.1737629850235305</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5080641700457871</v>
+        <v>0.5012899811118433</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1684591948629335</v>
+        <v>0.1970541462642775</v>
       </c>
       <c r="C77">
-        <v>-1.087148196616272</v>
+        <v>-1.460624029652815</v>
       </c>
       <c r="D77">
-        <v>2.080312544378277</v>
+        <v>1.772669521221662</v>
       </c>
       <c r="E77">
-        <v>4.404179753001817</v>
+        <v>4.470012562881744</v>
       </c>
       <c r="F77">
-        <v>4.937460740994549</v>
+        <v>5.003293550874477</v>
       </c>
       <c r="G77">
         <v>1.77</v>
@@ -7595,45 +7595,45 @@
         <v>0.497</v>
       </c>
       <c r="M77">
-        <v>0.9914421167917055</v>
+        <v>1.179776619296202</v>
       </c>
       <c r="N77">
-        <v>-0.4944421167917055</v>
+        <v>-0.6827766192962018</v>
       </c>
       <c r="O77">
-        <v>-0.1328071525702521</v>
+        <v>-0.1833937999429598</v>
       </c>
       <c r="P77">
-        <v>-0.3616349642214534</v>
+        <v>-0.499382819353242</v>
       </c>
       <c r="Q77">
-        <v>-0.2816349642214534</v>
+        <v>-0.4193828193532421</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1525478243811425</v>
+        <v>0.1588496145692903</v>
       </c>
       <c r="T77">
-        <v>2.080713786809503</v>
+        <v>2.203547407092412</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1346464889266411</v>
+        <v>0.1131520983011481</v>
       </c>
       <c r="W77">
-        <v>0.1737629850235305</v>
+        <v>0.2091187352205893</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5012899811118433</v>
+        <v>0.4212661887607896</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1970541462642775</v>
+        <v>0.1989541462642775</v>
       </c>
       <c r="C78">
-        <v>-1.460624029652815</v>
+        <v>-1.543705838336147</v>
       </c>
       <c r="D78">
-        <v>1.772669521221662</v>
+        <v>1.755420522418256</v>
       </c>
       <c r="E78">
-        <v>4.470012562881744</v>
+        <v>4.535845372761671</v>
       </c>
       <c r="F78">
-        <v>5.003293550874477</v>
+        <v>5.069126360754404</v>
       </c>
       <c r="G78">
         <v>1.77</v>
@@ -7677,37 +7677,37 @@
         <v>0.497</v>
       </c>
       <c r="M78">
-        <v>1.179776619296202</v>
+        <v>1.195299995865889</v>
       </c>
       <c r="N78">
-        <v>-0.6827766192962018</v>
+        <v>-0.6982999958658885</v>
       </c>
       <c r="O78">
-        <v>-0.1833937999429598</v>
+        <v>-0.1875633788895777</v>
       </c>
       <c r="P78">
-        <v>-0.499382819353242</v>
+        <v>-0.5107366169763109</v>
       </c>
       <c r="Q78">
-        <v>-0.4193828193532421</v>
+        <v>-0.4307366169763109</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1588496145692903</v>
+        <v>0.1637648152027377</v>
       </c>
       <c r="T78">
-        <v>2.203547407092412</v>
+        <v>2.29935381609643</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1131520983011481</v>
+        <v>0.1116825905310033</v>
       </c>
       <c r="W78">
-        <v>0.2091187352205893</v>
+        <v>0.2094652451527894</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4212661887607896</v>
+        <v>0.4157951992963639</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1989541462642775</v>
+        <v>0.2008541462642775</v>
       </c>
       <c r="C79">
-        <v>-1.543705838336147</v>
+        <v>-1.626455198412025</v>
       </c>
       <c r="D79">
-        <v>1.755420522418256</v>
+        <v>1.738503972222306</v>
       </c>
       <c r="E79">
-        <v>4.535845372761671</v>
+        <v>4.601678182641598</v>
       </c>
       <c r="F79">
-        <v>5.069126360754404</v>
+        <v>5.134959170634331</v>
       </c>
       <c r="G79">
         <v>1.77</v>
@@ -7759,37 +7759,37 @@
         <v>0.497</v>
       </c>
       <c r="M79">
-        <v>1.195299995865889</v>
+        <v>1.210823372435575</v>
       </c>
       <c r="N79">
-        <v>-0.6982999958658885</v>
+        <v>-0.7138233724355753</v>
       </c>
       <c r="O79">
-        <v>-0.1875633788895777</v>
+        <v>-0.1917329578361955</v>
       </c>
       <c r="P79">
-        <v>-0.5107366169763109</v>
+        <v>-0.5220904145993798</v>
       </c>
       <c r="Q79">
-        <v>-0.4307366169763109</v>
+        <v>-0.4420904145993798</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1637648152027377</v>
+        <v>0.1691268522574076</v>
       </c>
       <c r="T79">
-        <v>2.29935381609643</v>
+        <v>2.403869898646267</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1116825905310033</v>
+        <v>0.1102507624472725</v>
       </c>
       <c r="W79">
-        <v>0.2094652451527894</v>
+        <v>0.2098028702149332</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4157951992963639</v>
+        <v>0.4104644916130772</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2008541462642775</v>
+        <v>0.2027541462642775</v>
       </c>
       <c r="C80">
-        <v>-1.626455198412025</v>
+        <v>-1.708881629317202</v>
       </c>
       <c r="D80">
-        <v>1.738503972222306</v>
+        <v>1.721910351197057</v>
       </c>
       <c r="E80">
-        <v>4.601678182641598</v>
+        <v>4.667510992521526</v>
       </c>
       <c r="F80">
-        <v>5.134959170634331</v>
+        <v>5.200791980514259</v>
       </c>
       <c r="G80">
         <v>1.77</v>
@@ -7841,37 +7841,37 @@
         <v>0.497</v>
       </c>
       <c r="M80">
-        <v>1.210823372435575</v>
+        <v>1.226346749005262</v>
       </c>
       <c r="N80">
-        <v>-0.7138233724355753</v>
+        <v>-0.7293467490052622</v>
       </c>
       <c r="O80">
-        <v>-0.1917329578361955</v>
+        <v>-0.1959025367828134</v>
       </c>
       <c r="P80">
-        <v>-0.5220904145993798</v>
+        <v>-0.5334442122224488</v>
       </c>
       <c r="Q80">
-        <v>-0.4420904145993798</v>
+        <v>-0.4534442122224488</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1691268522574076</v>
+        <v>0.1749995595077604</v>
       </c>
       <c r="T80">
-        <v>2.403869898646267</v>
+        <v>2.5183398938199</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1102507624472725</v>
+        <v>0.1088551831757881</v>
       </c>
       <c r="W80">
-        <v>0.2098028702149332</v>
+        <v>0.2101319478071492</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4104644916130772</v>
+        <v>0.4052687385546838</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2027541462642775</v>
+        <v>0.2046541462642775</v>
       </c>
       <c r="C81">
-        <v>-1.708881629317202</v>
+        <v>-1.790994290481266</v>
       </c>
       <c r="D81">
-        <v>1.721910351197057</v>
+        <v>1.70563049991292</v>
       </c>
       <c r="E81">
-        <v>4.667510992521526</v>
+        <v>4.733343802401453</v>
       </c>
       <c r="F81">
-        <v>5.200791980514259</v>
+        <v>5.266624790394186</v>
       </c>
       <c r="G81">
         <v>1.77</v>
@@ -7923,37 +7923,37 @@
         <v>0.497</v>
       </c>
       <c r="M81">
-        <v>1.226346749005262</v>
+        <v>1.241870125574949</v>
       </c>
       <c r="N81">
-        <v>-0.7293467490052622</v>
+        <v>-0.7448701255749491</v>
       </c>
       <c r="O81">
-        <v>-0.1959025367828134</v>
+        <v>-0.2000721157294313</v>
       </c>
       <c r="P81">
-        <v>-0.5334442122224488</v>
+        <v>-0.5447980098455178</v>
       </c>
       <c r="Q81">
-        <v>-0.4534442122224488</v>
+        <v>-0.4647980098455179</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1749995595077604</v>
+        <v>0.1814595374831484</v>
       </c>
       <c r="T81">
-        <v>2.5183398938199</v>
+        <v>2.644256888510895</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1088551831757881</v>
+        <v>0.1074944933860907</v>
       </c>
       <c r="W81">
-        <v>0.2101319478071492</v>
+        <v>0.2104527984595598</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4052687385546838</v>
+        <v>0.4002028793227502</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2046541462642775</v>
+        <v>0.2065541462642775</v>
       </c>
       <c r="C82">
-        <v>-1.790994290481266</v>
+        <v>-1.872801998185743</v>
       </c>
       <c r="D82">
-        <v>1.70563049991292</v>
+        <v>1.68965560208837</v>
       </c>
       <c r="E82">
-        <v>4.733343802401453</v>
+        <v>4.799176612281381</v>
       </c>
       <c r="F82">
-        <v>5.266624790394186</v>
+        <v>5.332457600274114</v>
       </c>
       <c r="G82">
         <v>1.77</v>
@@ -8005,37 +8005,37 @@
         <v>0.497</v>
       </c>
       <c r="M82">
-        <v>1.241870125574949</v>
+        <v>1.257393502144636</v>
       </c>
       <c r="N82">
-        <v>-0.7448701255749491</v>
+        <v>-0.7603935021446361</v>
       </c>
       <c r="O82">
-        <v>-0.2000721157294313</v>
+        <v>-0.2042416946760492</v>
       </c>
       <c r="P82">
-        <v>-0.5447980098455178</v>
+        <v>-0.5561518074685868</v>
       </c>
       <c r="Q82">
-        <v>-0.4647980098455179</v>
+        <v>-0.4761518074685869</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1814595374831484</v>
+        <v>0.1885995131401562</v>
       </c>
       <c r="T82">
-        <v>2.644256888510895</v>
+        <v>2.783428303695679</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1074944933860907</v>
+        <v>0.1061674008751513</v>
       </c>
       <c r="W82">
-        <v>0.2104527984595598</v>
+        <v>0.2107657268736393</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4002028793227502</v>
+        <v>0.395262103034815</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2065541462642775</v>
+        <v>0.2084541462642776</v>
       </c>
       <c r="C83">
-        <v>-1.872801998185743</v>
+        <v>-1.954313241484567</v>
       </c>
       <c r="D83">
-        <v>1.68965560208837</v>
+        <v>1.673977168669474</v>
       </c>
       <c r="E83">
-        <v>4.799176612281381</v>
+        <v>4.865009422161308</v>
       </c>
       <c r="F83">
-        <v>5.332457600274114</v>
+        <v>5.398290410154041</v>
       </c>
       <c r="G83">
         <v>1.77</v>
@@ -8087,37 +8087,37 @@
         <v>0.497</v>
       </c>
       <c r="M83">
-        <v>1.257393502144636</v>
+        <v>1.272916878714323</v>
       </c>
       <c r="N83">
-        <v>-0.7603935021446361</v>
+        <v>-0.7759168787143228</v>
       </c>
       <c r="O83">
-        <v>-0.2042416946760492</v>
+        <v>-0.2084112736226671</v>
       </c>
       <c r="P83">
-        <v>-0.5561518074685868</v>
+        <v>-0.5675056050916557</v>
       </c>
       <c r="Q83">
-        <v>-0.4761518074685869</v>
+        <v>-0.4875056050916557</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1885995131401562</v>
+        <v>0.1965328194257204</v>
       </c>
       <c r="T83">
-        <v>2.783428303695679</v>
+        <v>2.93806320945655</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1061674008751513</v>
+        <v>0.1048726764742348</v>
       </c>
       <c r="W83">
-        <v>0.2107657268736393</v>
+        <v>0.2110710228873754</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.395262103034815</v>
+        <v>0.39044183348561</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2084541462642776</v>
+        <v>0.2103541462642776</v>
       </c>
       <c r="C84">
-        <v>-1.954313241484567</v>
+        <v>-2.035536197246343</v>
       </c>
       <c r="D84">
-        <v>1.673977168669474</v>
+        <v>1.658587022787626</v>
       </c>
       <c r="E84">
-        <v>4.865009422161308</v>
+        <v>4.930842232041236</v>
       </c>
       <c r="F84">
-        <v>5.398290410154041</v>
+        <v>5.464123220033969</v>
       </c>
       <c r="G84">
         <v>1.77</v>
@@ -8169,37 +8169,37 @@
         <v>0.497</v>
       </c>
       <c r="M84">
-        <v>1.272916878714323</v>
+        <v>1.28844025528401</v>
       </c>
       <c r="N84">
-        <v>-0.7759168787143228</v>
+        <v>-0.79144025528401</v>
       </c>
       <c r="O84">
-        <v>-0.2084112736226671</v>
+        <v>-0.2125808525692851</v>
       </c>
       <c r="P84">
-        <v>-0.5675056050916557</v>
+        <v>-0.5788594027147249</v>
       </c>
       <c r="Q84">
-        <v>-0.4875056050916557</v>
+        <v>-0.498859402714725</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1965328194257204</v>
+        <v>0.2053994558625275</v>
       </c>
       <c r="T84">
-        <v>2.93806320945655</v>
+        <v>3.110890457071642</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1048726764742348</v>
+        <v>0.1036091502516537</v>
       </c>
       <c r="W84">
-        <v>0.2110710228873754</v>
+        <v>0.2113689623706601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.39044183348561</v>
+        <v>0.3857377150098796</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2103541462642776</v>
+        <v>0.2122541462642775</v>
       </c>
       <c r="C85">
-        <v>-2.035536197246343</v>
+        <v>-2.116478744374395</v>
       </c>
       <c r="D85">
-        <v>1.658587022787626</v>
+        <v>1.643477285539501</v>
       </c>
       <c r="E85">
-        <v>4.930842232041236</v>
+        <v>4.996675041921163</v>
       </c>
       <c r="F85">
-        <v>5.464123220033969</v>
+        <v>5.529956029913896</v>
       </c>
       <c r="G85">
         <v>1.77</v>
@@ -8251,37 +8251,37 @@
         <v>0.497</v>
       </c>
       <c r="M85">
-        <v>1.28844025528401</v>
+        <v>1.303963631853697</v>
       </c>
       <c r="N85">
-        <v>-0.79144025528401</v>
+        <v>-0.8069636318536967</v>
       </c>
       <c r="O85">
-        <v>-0.2125808525692851</v>
+        <v>-0.2167504315159029</v>
       </c>
       <c r="P85">
-        <v>-0.5788594027147249</v>
+        <v>-0.5902132003377938</v>
       </c>
       <c r="Q85">
-        <v>-0.498859402714725</v>
+        <v>-0.5102132003377938</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2053994558625275</v>
+        <v>0.2153744218539355</v>
       </c>
       <c r="T85">
-        <v>3.110890457071642</v>
+        <v>3.30532111063862</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1036091502516537</v>
+        <v>0.102375707986753</v>
       </c>
       <c r="W85">
-        <v>0.2113689623706601</v>
+        <v>0.2116598080567237</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3857377150098796</v>
+        <v>0.3811455993550001</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2122541462642775</v>
+        <v>0.2141541462642775</v>
       </c>
       <c r="C86">
-        <v>-2.116478744374394</v>
+        <v>-2.197148477256571</v>
       </c>
       <c r="D86">
-        <v>1.643477285539501</v>
+        <v>1.628640362537252</v>
       </c>
       <c r="E86">
-        <v>4.996675041921162</v>
+        <v>5.06250785180109</v>
       </c>
       <c r="F86">
-        <v>5.529956029913895</v>
+        <v>5.595788839793823</v>
       </c>
       <c r="G86">
         <v>1.77</v>
@@ -8333,37 +8333,37 @@
         <v>0.497</v>
       </c>
       <c r="M86">
-        <v>1.303963631853696</v>
+        <v>1.319487008423383</v>
       </c>
       <c r="N86">
-        <v>-0.8069636318536965</v>
+        <v>-0.8224870084233834</v>
       </c>
       <c r="O86">
-        <v>-0.2167504315159029</v>
+        <v>-0.2209200104625208</v>
       </c>
       <c r="P86">
-        <v>-0.5902132003377936</v>
+        <v>-0.6015669979608627</v>
       </c>
       <c r="Q86">
-        <v>-0.5102132003377936</v>
+        <v>-0.5215669979608627</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2153744218539354</v>
+        <v>0.2266793833108644</v>
       </c>
       <c r="T86">
-        <v>3.305321110638618</v>
+        <v>3.525675851347859</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1023757079867531</v>
+        <v>0.1011712878927913</v>
       </c>
       <c r="W86">
-        <v>0.2116598080567236</v>
+        <v>0.2119438103148798</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3811455993550003</v>
+        <v>0.3766615334802355</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2141541462642775</v>
+        <v>0.2160541462642775</v>
       </c>
       <c r="C87">
-        <v>-2.197148477256571</v>
+        <v>-2.277552718493025</v>
       </c>
       <c r="D87">
-        <v>1.628640362537252</v>
+        <v>1.614068931180725</v>
       </c>
       <c r="E87">
-        <v>5.06250785180109</v>
+        <v>5.128340661681017</v>
       </c>
       <c r="F87">
-        <v>5.595788839793823</v>
+        <v>5.66162164967375</v>
       </c>
       <c r="G87">
         <v>1.77</v>
@@ -8415,37 +8415,37 @@
         <v>0.497</v>
       </c>
       <c r="M87">
-        <v>1.319487008423383</v>
+        <v>1.33501038499307</v>
       </c>
       <c r="N87">
-        <v>-0.8224870084233834</v>
+        <v>-0.8380103849930703</v>
       </c>
       <c r="O87">
-        <v>-0.2209200104625208</v>
+        <v>-0.2250895894091387</v>
       </c>
       <c r="P87">
-        <v>-0.6015669979608627</v>
+        <v>-0.6129207955839316</v>
       </c>
       <c r="Q87">
-        <v>-0.5215669979608627</v>
+        <v>-0.5329207955839317</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2266793833108644</v>
+        <v>0.2395993392616405</v>
       </c>
       <c r="T87">
-        <v>3.525675851347859</v>
+        <v>3.777509840729849</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1011712878927913</v>
+        <v>0.09999487756845647</v>
       </c>
       <c r="W87">
-        <v>0.2119438103148798</v>
+        <v>0.212221207869358</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3766615334802355</v>
+        <v>0.3722817482072095</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2160541462642775</v>
+        <v>0.2179541462642776</v>
       </c>
       <c r="C88">
-        <v>-2.277552718493025</v>
+        <v>-2.357698530946815</v>
       </c>
       <c r="D88">
-        <v>1.614068931180725</v>
+        <v>1.599755928606862</v>
       </c>
       <c r="E88">
-        <v>5.128340661681017</v>
+        <v>5.194173471560944</v>
       </c>
       <c r="F88">
-        <v>5.66162164967375</v>
+        <v>5.727454459553677</v>
       </c>
       <c r="G88">
         <v>1.77</v>
@@ -8497,37 +8497,37 @@
         <v>0.497</v>
       </c>
       <c r="M88">
-        <v>1.33501038499307</v>
+        <v>1.350533761562757</v>
       </c>
       <c r="N88">
-        <v>-0.8380103849930703</v>
+        <v>-0.8535337615627571</v>
       </c>
       <c r="O88">
-        <v>-0.2250895894091387</v>
+        <v>-0.2292591683557565</v>
       </c>
       <c r="P88">
-        <v>-0.6129207955839316</v>
+        <v>-0.6242745932070005</v>
       </c>
       <c r="Q88">
-        <v>-0.5329207955839317</v>
+        <v>-0.5442745932070006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2395993392616405</v>
+        <v>0.2545069807433051</v>
       </c>
       <c r="T88">
-        <v>3.777509840729849</v>
+        <v>4.068087520785991</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09999487756845647</v>
+        <v>0.09884551115962364</v>
       </c>
       <c r="W88">
-        <v>0.212221207869358</v>
+        <v>0.2124922284685608</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3722817482072095</v>
+        <v>0.3680026476531036</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2179541462642776</v>
+        <v>0.2198541462642775</v>
       </c>
       <c r="C89">
-        <v>-2.357698530946815</v>
+        <v>-2.437592729158967</v>
       </c>
       <c r="D89">
-        <v>1.599755928606862</v>
+        <v>1.585694540274638</v>
       </c>
       <c r="E89">
-        <v>5.194173471560944</v>
+        <v>5.260006281440872</v>
       </c>
       <c r="F89">
-        <v>5.727454459553677</v>
+        <v>5.793287269433605</v>
       </c>
       <c r="G89">
         <v>1.77</v>
@@ -8579,37 +8579,37 @@
         <v>0.497</v>
       </c>
       <c r="M89">
-        <v>1.350533761562757</v>
+        <v>1.366057138132444</v>
       </c>
       <c r="N89">
-        <v>-0.8535337615627571</v>
+        <v>-0.869057138132444</v>
       </c>
       <c r="O89">
-        <v>-0.2292591683557565</v>
+        <v>-0.2334287473023745</v>
       </c>
       <c r="P89">
-        <v>-0.6242745932070005</v>
+        <v>-0.6356283908300695</v>
       </c>
       <c r="Q89">
-        <v>-0.5442745932070006</v>
+        <v>-0.5556283908300695</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2545069807433051</v>
+        <v>0.2718992291385806</v>
       </c>
       <c r="T89">
-        <v>4.068087520785991</v>
+        <v>4.407094814184824</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09884551115962364</v>
+        <v>0.09772226671462791</v>
       </c>
       <c r="W89">
-        <v>0.2124922284685608</v>
+        <v>0.2127570895086907</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3680026476531036</v>
+        <v>0.3638207993843183</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2198541462642775</v>
+        <v>0.2217541462642775</v>
       </c>
       <c r="C90">
-        <v>-2.437592729158967</v>
+        <v>-2.517241890166778</v>
       </c>
       <c r="D90">
-        <v>1.585694540274638</v>
+        <v>1.571878189146754</v>
       </c>
       <c r="E90">
-        <v>5.260006281440872</v>
+        <v>5.325839091320799</v>
       </c>
       <c r="F90">
-        <v>5.793287269433605</v>
+        <v>5.859120079313532</v>
       </c>
       <c r="G90">
         <v>1.77</v>
@@ -8661,37 +8661,37 @@
         <v>0.497</v>
       </c>
       <c r="M90">
-        <v>1.366057138132444</v>
+        <v>1.381580514702131</v>
       </c>
       <c r="N90">
-        <v>-0.869057138132444</v>
+        <v>-0.8845805147021307</v>
       </c>
       <c r="O90">
-        <v>-0.2334287473023745</v>
+        <v>-0.2375983262489923</v>
       </c>
       <c r="P90">
-        <v>-0.6356283908300695</v>
+        <v>-0.6469821884531384</v>
       </c>
       <c r="Q90">
-        <v>-0.5556283908300695</v>
+        <v>-0.5669821884531384</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2718992291385806</v>
+        <v>0.2924537045148151</v>
       </c>
       <c r="T90">
-        <v>4.407094814184824</v>
+        <v>4.807739797292535</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09772226671462791</v>
+        <v>0.09662426371783435</v>
       </c>
       <c r="W90">
-        <v>0.2127570895086907</v>
+        <v>0.2130159986153347</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3638207993843183</v>
+        <v>0.3597329252339329</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2217541462642775</v>
+        <v>0.2236541462642775</v>
       </c>
       <c r="C91">
-        <v>-2.517241890166778</v>
+        <v>-2.596652363761438</v>
       </c>
       <c r="D91">
-        <v>1.571878189146754</v>
+        <v>1.558300525432022</v>
       </c>
       <c r="E91">
-        <v>5.325839091320799</v>
+        <v>5.391671901200727</v>
       </c>
       <c r="F91">
-        <v>5.859120079313532</v>
+        <v>5.92495288919346</v>
       </c>
       <c r="G91">
         <v>1.77</v>
@@ -8743,37 +8743,37 @@
         <v>0.497</v>
       </c>
       <c r="M91">
-        <v>1.381580514702131</v>
+        <v>1.397103891271818</v>
       </c>
       <c r="N91">
-        <v>-0.8845805147021307</v>
+        <v>-0.9001038912718179</v>
       </c>
       <c r="O91">
-        <v>-0.2375983262489923</v>
+        <v>-0.2417679051956103</v>
       </c>
       <c r="P91">
-        <v>-0.6469821884531384</v>
+        <v>-0.6583359860762076</v>
       </c>
       <c r="Q91">
-        <v>-0.5669821884531384</v>
+        <v>-0.5783359860762076</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2924537045148151</v>
+        <v>0.3171190749662968</v>
       </c>
       <c r="T91">
-        <v>4.807739797292535</v>
+        <v>5.28851377702179</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09662426371783435</v>
+        <v>0.09555066078763617</v>
       </c>
       <c r="W91">
-        <v>0.2130159986153347</v>
+        <v>0.2132691541862754</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3597329252339329</v>
+        <v>0.3557358927313334</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2236541462642775</v>
+        <v>0.2255541462642776</v>
       </c>
       <c r="C92">
-        <v>-2.596652363761438</v>
+        <v>-2.675830282218572</v>
       </c>
       <c r="D92">
-        <v>1.558300525432022</v>
+        <v>1.544955416854815</v>
       </c>
       <c r="E92">
-        <v>5.391671901200727</v>
+        <v>5.457504711080654</v>
       </c>
       <c r="F92">
-        <v>5.92495288919346</v>
+        <v>5.990785699073387</v>
       </c>
       <c r="G92">
         <v>1.77</v>
@@ -8825,37 +8825,37 @@
         <v>0.497</v>
       </c>
       <c r="M92">
-        <v>1.397103891271818</v>
+        <v>1.412627267841505</v>
       </c>
       <c r="N92">
-        <v>-0.9001038912718179</v>
+        <v>-0.9156272678415046</v>
       </c>
       <c r="O92">
-        <v>-0.2417679051956103</v>
+        <v>-0.2459374841422281</v>
       </c>
       <c r="P92">
-        <v>-0.6583359860762076</v>
+        <v>-0.6696897836992765</v>
       </c>
       <c r="Q92">
-        <v>-0.5783359860762076</v>
+        <v>-0.5896897836992765</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3171190749662968</v>
+        <v>0.3472656388514408</v>
       </c>
       <c r="T92">
-        <v>5.28851377702179</v>
+        <v>5.8761264189131</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09555066078763617</v>
+        <v>0.09450065352623359</v>
       </c>
       <c r="W92">
-        <v>0.2132691541862754</v>
+        <v>0.2135167458985141</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3557358927313334</v>
+        <v>0.3518267070969232</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2255541462642776</v>
+        <v>0.2274541462642775</v>
       </c>
       <c r="C93">
-        <v>-2.675830282218572</v>
+        <v>-2.754781569533058</v>
       </c>
       <c r="D93">
-        <v>1.544955416854815</v>
+        <v>1.531836939420256</v>
       </c>
       <c r="E93">
-        <v>5.457504711080654</v>
+        <v>5.523337520960581</v>
       </c>
       <c r="F93">
-        <v>5.990785699073387</v>
+        <v>6.056618508953314</v>
       </c>
       <c r="G93">
         <v>1.77</v>
@@ -8907,37 +8907,37 @@
         <v>0.497</v>
       </c>
       <c r="M93">
-        <v>1.412627267841505</v>
+        <v>1.428150644411191</v>
       </c>
       <c r="N93">
-        <v>-0.9156272678415046</v>
+        <v>-0.9311506444111913</v>
       </c>
       <c r="O93">
-        <v>-0.2459374841422281</v>
+        <v>-0.250107063088846</v>
       </c>
       <c r="P93">
-        <v>-0.6696897836992765</v>
+        <v>-0.6810435813223453</v>
       </c>
       <c r="Q93">
-        <v>-0.5896897836992765</v>
+        <v>-0.6010435813223454</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3472656388514408</v>
+        <v>0.3849488437078711</v>
       </c>
       <c r="T93">
-        <v>5.8761264189131</v>
+        <v>6.61064222127724</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09450065352623359</v>
+        <v>0.09347347250964409</v>
       </c>
       <c r="W93">
-        <v>0.2135167458985141</v>
+        <v>0.2137589551822259</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3518267070969232</v>
+        <v>0.3480025037589133</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2274541462642775</v>
+        <v>0.2293541462642775</v>
       </c>
       <c r="C94">
-        <v>-2.754781569533058</v>
+        <v>-2.833511950187298</v>
       </c>
       <c r="D94">
-        <v>1.531836939420256</v>
+        <v>1.518939368645943</v>
       </c>
       <c r="E94">
-        <v>5.523337520960581</v>
+        <v>5.589170330840509</v>
       </c>
       <c r="F94">
-        <v>6.056618508953314</v>
+        <v>6.122451318833241</v>
       </c>
       <c r="G94">
         <v>1.77</v>
@@ -8989,37 +8989,37 @@
         <v>0.497</v>
       </c>
       <c r="M94">
-        <v>1.428150644411191</v>
+        <v>1.443674020980878</v>
       </c>
       <c r="N94">
-        <v>-0.9311506444111913</v>
+        <v>-0.9466740209808785</v>
       </c>
       <c r="O94">
-        <v>-0.250107063088846</v>
+        <v>-0.254276642035464</v>
       </c>
       <c r="P94">
-        <v>-0.6810435813223453</v>
+        <v>-0.6923973789454145</v>
       </c>
       <c r="Q94">
-        <v>-0.6010435813223454</v>
+        <v>-0.6123973789454146</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3849488437078711</v>
+        <v>0.4333986785232812</v>
       </c>
       <c r="T94">
-        <v>6.61064222127724</v>
+        <v>7.555019681459703</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09347347250964409</v>
+        <v>0.09246838140738985</v>
       </c>
       <c r="W94">
-        <v>0.2137589551822259</v>
+        <v>0.2139959556641375</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3480025037589133</v>
+        <v>0.3442605413529034</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2293541462642775</v>
+        <v>0.2312541462642776</v>
       </c>
       <c r="C95">
-        <v>-2.833511950187298</v>
+        <v>-2.912026957480252</v>
       </c>
       <c r="D95">
-        <v>1.518939368645943</v>
+        <v>1.506257171232916</v>
       </c>
       <c r="E95">
-        <v>5.589170330840509</v>
+        <v>5.655003140720436</v>
       </c>
       <c r="F95">
-        <v>6.122451318833241</v>
+        <v>6.188284128713168</v>
       </c>
       <c r="G95">
         <v>1.77</v>
@@ -9071,37 +9071,37 @@
         <v>0.497</v>
       </c>
       <c r="M95">
-        <v>1.443674020980878</v>
+        <v>1.459197397550565</v>
       </c>
       <c r="N95">
-        <v>-0.9466740209808785</v>
+        <v>-0.9621973975505652</v>
       </c>
       <c r="O95">
-        <v>-0.254276642035464</v>
+        <v>-0.2584462209820818</v>
       </c>
       <c r="P95">
-        <v>-0.6923973789454145</v>
+        <v>-0.7037511765684834</v>
       </c>
       <c r="Q95">
-        <v>-0.6123973789454146</v>
+        <v>-0.6237511765684834</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4333986785232812</v>
+        <v>0.4979984582771615</v>
       </c>
       <c r="T95">
-        <v>7.555019681459703</v>
+        <v>8.814189628369656</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09246838140738985</v>
+        <v>0.09148467522220485</v>
       </c>
       <c r="W95">
-        <v>0.2139959556641375</v>
+        <v>0.2142279135826041</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3442605413529034</v>
+        <v>0.340598195168298</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2312541462642776</v>
+        <v>0.2331541462642776</v>
       </c>
       <c r="C96">
-        <v>-2.912026957480252</v>
+        <v>-2.990331941442657</v>
       </c>
       <c r="D96">
-        <v>1.506257171232916</v>
+        <v>1.49378499715044</v>
       </c>
       <c r="E96">
-        <v>5.655003140720436</v>
+        <v>5.720835950600364</v>
       </c>
       <c r="F96">
-        <v>6.188284128713168</v>
+        <v>6.254116938593096</v>
       </c>
       <c r="G96">
         <v>1.77</v>
@@ -9153,37 +9153,37 @@
         <v>0.497</v>
       </c>
       <c r="M96">
-        <v>1.459197397550565</v>
+        <v>1.474720774120252</v>
       </c>
       <c r="N96">
-        <v>-0.9621973975505652</v>
+        <v>-0.9777207741202522</v>
       </c>
       <c r="O96">
-        <v>-0.2584462209820818</v>
+        <v>-0.2626157999286997</v>
       </c>
       <c r="P96">
-        <v>-0.7037511765684834</v>
+        <v>-0.7151049741915525</v>
       </c>
       <c r="Q96">
-        <v>-0.6237511765684834</v>
+        <v>-0.6351049741915525</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4979984582771615</v>
+        <v>0.5884381499325941</v>
       </c>
       <c r="T96">
-        <v>8.814189628369656</v>
+        <v>10.57702755404359</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09148467522220485</v>
+        <v>0.09052167864091848</v>
       </c>
       <c r="W96">
-        <v>0.2142279135826041</v>
+        <v>0.2144549881764714</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.340598195168298</v>
+        <v>0.3370129510086317</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2331541462642776</v>
+        <v>0.2350541462642775</v>
       </c>
       <c r="C97">
-        <v>-2.990331941442657</v>
+        <v>-3.068432076362242</v>
       </c>
       <c r="D97">
-        <v>1.49378499715044</v>
+        <v>1.481517672110781</v>
       </c>
       <c r="E97">
-        <v>5.720835950600364</v>
+        <v>5.786668760480291</v>
       </c>
       <c r="F97">
-        <v>6.254116938593096</v>
+        <v>6.319949748473023</v>
       </c>
       <c r="G97">
         <v>1.77</v>
@@ -9235,37 +9235,37 @@
         <v>0.497</v>
       </c>
       <c r="M97">
-        <v>1.474720774120252</v>
+        <v>1.490244150689939</v>
       </c>
       <c r="N97">
-        <v>-0.9777207741202522</v>
+        <v>-0.9932441506899389</v>
       </c>
       <c r="O97">
-        <v>-0.2626157999286997</v>
+        <v>-0.2667853788753176</v>
       </c>
       <c r="P97">
-        <v>-0.7151049741915525</v>
+        <v>-0.7264587718146213</v>
       </c>
       <c r="Q97">
-        <v>-0.6351049741915525</v>
+        <v>-0.6464587718146213</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5884381499325941</v>
+        <v>0.724097687415743</v>
       </c>
       <c r="T97">
-        <v>10.57702755404359</v>
+        <v>13.2212844425545</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09052167864091848</v>
+        <v>0.08957874448840893</v>
       </c>
       <c r="W97">
-        <v>0.2144549881764714</v>
+        <v>0.2146773320496332</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3370129510086317</v>
+        <v>0.3335023994356252</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2350541462642775</v>
+        <v>0.2369541462642775</v>
       </c>
       <c r="C98">
-        <v>-3.068432076362241</v>
+        <v>-3.14633236794118</v>
       </c>
       <c r="D98">
-        <v>1.481517672110781</v>
+        <v>1.46945019041177</v>
       </c>
       <c r="E98">
-        <v>5.78666876048029</v>
+        <v>5.852501570360218</v>
       </c>
       <c r="F98">
-        <v>6.319949748473022</v>
+        <v>6.38578255835295</v>
       </c>
       <c r="G98">
         <v>1.77</v>
@@ -9317,37 +9317,37 @@
         <v>0.497</v>
       </c>
       <c r="M98">
-        <v>1.490244150689939</v>
+        <v>1.505767527259626</v>
       </c>
       <c r="N98">
-        <v>-0.9932441506899389</v>
+        <v>-1.008767527259626</v>
       </c>
       <c r="O98">
-        <v>-0.2667853788753176</v>
+        <v>-0.2709549578219355</v>
       </c>
       <c r="P98">
-        <v>-0.7264587718146213</v>
+        <v>-0.7378125694376905</v>
       </c>
       <c r="Q98">
-        <v>-0.6464587718146213</v>
+        <v>-0.6578125694376905</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.724097687415741</v>
+        <v>0.9501969165543216</v>
       </c>
       <c r="T98">
-        <v>13.22128444255446</v>
+        <v>17.62837925673928</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08957874448840893</v>
+        <v>0.08865525227718821</v>
       </c>
       <c r="W98">
-        <v>0.2146773320496332</v>
+        <v>0.214895091513039</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3335023994356252</v>
+        <v>0.3300642303692785</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2369541462642775</v>
+        <v>0.2388541462642775</v>
       </c>
       <c r="C99">
-        <v>-3.14633236794118</v>
+        <v>-3.224037660106545</v>
       </c>
       <c r="D99">
-        <v>1.46945019041177</v>
+        <v>1.457577708126332</v>
       </c>
       <c r="E99">
-        <v>5.852501570360218</v>
+        <v>5.918334380240145</v>
       </c>
       <c r="F99">
-        <v>6.38578255835295</v>
+        <v>6.451615368232877</v>
       </c>
       <c r="G99">
         <v>1.77</v>
@@ -9399,37 +9399,37 @@
         <v>0.497</v>
       </c>
       <c r="M99">
-        <v>1.505767527259626</v>
+        <v>1.521290903829313</v>
       </c>
       <c r="N99">
-        <v>-1.008767527259626</v>
+        <v>-1.024290903829312</v>
       </c>
       <c r="O99">
-        <v>-0.2709549578219355</v>
+        <v>-0.2751245367685533</v>
       </c>
       <c r="P99">
-        <v>-0.7378125694376905</v>
+        <v>-0.7491663670607591</v>
       </c>
       <c r="Q99">
-        <v>-0.6578125694376905</v>
+        <v>-0.6691663670607592</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9501969165543216</v>
+        <v>1.402395374831482</v>
       </c>
       <c r="T99">
-        <v>17.62837925673928</v>
+        <v>26.44256888510892</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08865525227718821</v>
+        <v>0.08775060684578834</v>
       </c>
       <c r="W99">
-        <v>0.214895091513039</v>
+        <v>0.2151084069057631</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3300642303692785</v>
+        <v>0.3266962280185717</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2388541462642775</v>
+        <v>0.2407541462642775</v>
       </c>
       <c r="C100">
-        <v>-3.224037660106545</v>
+        <v>-3.301552641493287</v>
       </c>
       <c r="D100">
-        <v>1.457577708126332</v>
+        <v>1.445895536619518</v>
       </c>
       <c r="E100">
-        <v>5.918334380240145</v>
+        <v>5.984167190120073</v>
       </c>
       <c r="F100">
-        <v>6.451615368232877</v>
+        <v>6.517448178112805</v>
       </c>
       <c r="G100">
         <v>1.77</v>
@@ -9481,37 +9481,37 @@
         <v>0.497</v>
       </c>
       <c r="M100">
-        <v>1.521290903829313</v>
+        <v>1.536814280398999</v>
       </c>
       <c r="N100">
-        <v>-1.024290903829312</v>
+        <v>-1.039814280398999</v>
       </c>
       <c r="O100">
-        <v>-0.2751245367685533</v>
+        <v>-0.2792941157151712</v>
       </c>
       <c r="P100">
-        <v>-0.7491663670607591</v>
+        <v>-0.7605201646838282</v>
       </c>
       <c r="Q100">
-        <v>-0.6691663670607592</v>
+        <v>-0.6805201646838283</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.402395374831482</v>
+        <v>2.758990749662964</v>
       </c>
       <c r="T100">
-        <v>26.44256888510892</v>
+        <v>52.88513777021784</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08775060684578834</v>
+        <v>0.08686423707966925</v>
       </c>
       <c r="W100">
-        <v>0.2151084069057631</v>
+        <v>0.215317412896614</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3266962280185717</v>
+        <v>0.3233962661193942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2407541462642775</v>
-      </c>
-      <c r="C101">
-        <v>-3.301552641493287</v>
-      </c>
-      <c r="D101">
-        <v>1.445895536619518</v>
-      </c>
-      <c r="E101">
-        <v>5.984167190120073</v>
-      </c>
-      <c r="F101">
-        <v>6.517448178112805</v>
-      </c>
-      <c r="G101">
-        <v>1.77</v>
-      </c>
-      <c r="H101">
-        <v>6.05</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.577</v>
-      </c>
-      <c r="K101">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="L101">
-        <v>0.497</v>
-      </c>
-      <c r="M101">
-        <v>1.536814280398999</v>
-      </c>
-      <c r="N101">
-        <v>-1.039814280398999</v>
-      </c>
-      <c r="O101">
-        <v>-0.2792941157151712</v>
-      </c>
-      <c r="P101">
-        <v>-0.7605201646838282</v>
-      </c>
-      <c r="Q101">
-        <v>-0.6805201646838283</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.758990749662964</v>
-      </c>
-      <c r="T101">
-        <v>52.88513777021784</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08686423707966925</v>
-      </c>
-      <c r="W101">
-        <v>0.215317412896614</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3233962661193942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
